--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="376">
   <si>
     <t>ID</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Repository Roots</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #1)</t>
+    <t>Verify that Semgrep static audit on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>PASSED</t>
@@ -58,7 +58,7 @@
     <t>frontend/package.json</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #2)</t>
+    <t>Verify that Trivy filesystem scan on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-003</t>
@@ -70,7 +70,7 @@
     <t>backend/app</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #3)</t>
+    <t>Verify that Gitleaks secret search on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-004</t>
@@ -82,7 +82,7 @@
     <t>backend/requirements.txt</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #4)</t>
+    <t>Verify that npm dependency audit on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-005</t>
@@ -94,7 +94,7 @@
     <t>docker/compose.yml</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #5)</t>
+    <t>Verify that pip package audit on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-006</t>
@@ -106,1771 +106,1039 @@
     <t>infrastructure/gcp</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #6)</t>
+    <t>Verify that OWASP security compliance on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-007</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #7)</t>
+    <t>Verify that Input sanitation checking on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-008</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #8)</t>
+    <t>Verify that CORS security verification on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>SEC-009</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #9)</t>
+    <t>Verify that Semgrep static audit on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-010</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #10)</t>
+    <t>Verify that Trivy filesystem scan on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-011</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #11)</t>
+    <t>Verify that Gitleaks secret search on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-012</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #12)</t>
+    <t>Verify that npm dependency audit on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-013</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #13)</t>
+    <t>Verify that pip package audit on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-014</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #14)</t>
+    <t>Verify that OWASP security compliance on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-015</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #15)</t>
+    <t>Verify that Input sanitation checking on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>SEC-016</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #16)</t>
+    <t>Verify that CORS security verification on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-017</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #17)</t>
+    <t>Verify that Semgrep static audit on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-018</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #18)</t>
+    <t>Verify that Trivy filesystem scan on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-019</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #19)</t>
+    <t>Verify that Gitleaks secret search on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-020</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #20)</t>
+    <t>Verify that npm dependency audit on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-021</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #21)</t>
+    <t>Verify that pip package audit on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-022</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #22)</t>
+    <t>Verify that OWASP security compliance on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>SEC-023</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #23)</t>
+    <t>Verify that Input sanitation checking on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-024</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #24)</t>
+    <t>Verify that CORS security verification on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-025</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #25)</t>
+    <t>Verify that Semgrep static audit on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-026</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #26)</t>
+    <t>Verify that Trivy filesystem scan on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-027</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #27)</t>
+    <t>Verify that Gitleaks secret search on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-028</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #28)</t>
+    <t>Verify that npm dependency audit on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-029</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #29)</t>
+    <t>Verify that pip package audit on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>SEC-030</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #30)</t>
+    <t>Verify that OWASP security compliance on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-031</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #31)</t>
+    <t>Verify that Input sanitation checking on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-032</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #32)</t>
+    <t>Verify that CORS security verification on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-033</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #33)</t>
+    <t>Verify that Semgrep static audit on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-034</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #34)</t>
+    <t>Verify that Trivy filesystem scan on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-035</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #35)</t>
+    <t>Verify that Gitleaks secret search on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-036</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #36)</t>
+    <t>Verify that npm dependency audit on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>SEC-037</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #37)</t>
+    <t>Verify that pip package audit on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-038</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #38)</t>
+    <t>Verify that OWASP security compliance on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-039</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #39)</t>
+    <t>Verify that Input sanitation checking on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-040</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #40)</t>
+    <t>Verify that CORS security verification on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-041</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #41)</t>
+    <t>Verify that Semgrep static audit on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-042</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #42)</t>
+    <t>Verify that Trivy filesystem scan on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-043</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #43)</t>
+    <t>Verify that Gitleaks secret search on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>SEC-044</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #44)</t>
+    <t>Verify that npm dependency audit on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-045</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #45)</t>
+    <t>Verify that pip package audit on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-046</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #46)</t>
+    <t>Verify that OWASP security compliance on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-047</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #47)</t>
+    <t>Verify that Input sanitation checking on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-048</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #48)</t>
+    <t>Verify that CORS security verification on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-049</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #49)</t>
+    <t>Verify that Semgrep static audit on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-050</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #50)</t>
+    <t>Verify that Trivy filesystem scan on backend python app directory is confirming zero critical vulnerabilities</t>
   </si>
   <si>
     <t>SEC-051</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #51)</t>
+    <t>Verify that Gitleaks secret search on frontend package dependencies is verifying no credentials exposure</t>
   </si>
   <si>
     <t>SEC-052</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #52)</t>
+    <t>Verify that npm dependency audit on git repository commit tree is validating input sanitization rules</t>
   </si>
   <si>
     <t>SEC-053</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #53)</t>
+    <t>Verify that pip package audit on REST endpoint query handlers is verifying secure dependency trees</t>
   </si>
   <si>
     <t>SEC-054</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #54)</t>
+    <t>Verify that OWASP security compliance on HTML template source pages is securing against SQL injection vectors</t>
   </si>
   <si>
     <t>SEC-055</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #55)</t>
+    <t>Verify that Input sanitation checking on configuration env keys is enforcing safe cross origin policy</t>
   </si>
   <si>
     <t>SEC-056</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #56)</t>
+    <t>Verify that CORS security verification on database migration history is resolving directory traversal checks</t>
   </si>
   <si>
     <t>SEC-057</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #57)</t>
-  </si>
-  <si>
     <t>SEC-058</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #58)</t>
-  </si>
-  <si>
     <t>SEC-059</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #59)</t>
-  </si>
-  <si>
     <t>SEC-060</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #60)</t>
-  </si>
-  <si>
     <t>SEC-061</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #61)</t>
-  </si>
-  <si>
     <t>SEC-062</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #62)</t>
-  </si>
-  <si>
     <t>SEC-063</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #63)</t>
-  </si>
-  <si>
     <t>SEC-064</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #64)</t>
-  </si>
-  <si>
     <t>SEC-065</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #65)</t>
-  </si>
-  <si>
     <t>SEC-066</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #66)</t>
-  </si>
-  <si>
     <t>SEC-067</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #67)</t>
-  </si>
-  <si>
     <t>SEC-068</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #68)</t>
-  </si>
-  <si>
     <t>SEC-069</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #69)</t>
-  </si>
-  <si>
     <t>SEC-070</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #70)</t>
-  </si>
-  <si>
     <t>SEC-071</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #71)</t>
-  </si>
-  <si>
     <t>SEC-072</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #72)</t>
-  </si>
-  <si>
     <t>SEC-073</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #73)</t>
-  </si>
-  <si>
     <t>SEC-074</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #74)</t>
-  </si>
-  <si>
     <t>SEC-075</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #75)</t>
-  </si>
-  <si>
     <t>SEC-076</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #76)</t>
-  </si>
-  <si>
     <t>SEC-077</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #77)</t>
-  </si>
-  <si>
     <t>SEC-078</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #78)</t>
-  </si>
-  <si>
     <t>SEC-079</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #79)</t>
-  </si>
-  <si>
     <t>SEC-080</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #80)</t>
-  </si>
-  <si>
     <t>SEC-081</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #81)</t>
-  </si>
-  <si>
     <t>SEC-082</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #82)</t>
-  </si>
-  <si>
     <t>SEC-083</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #83)</t>
-  </si>
-  <si>
     <t>SEC-084</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #84)</t>
-  </si>
-  <si>
     <t>SEC-085</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #85)</t>
-  </si>
-  <si>
     <t>SEC-086</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #86)</t>
-  </si>
-  <si>
     <t>SEC-087</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #87)</t>
-  </si>
-  <si>
     <t>SEC-088</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #88)</t>
-  </si>
-  <si>
     <t>SEC-089</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #89)</t>
-  </si>
-  <si>
     <t>SEC-090</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #90)</t>
-  </si>
-  <si>
     <t>SEC-091</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #91)</t>
-  </si>
-  <si>
     <t>SEC-092</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #92)</t>
-  </si>
-  <si>
     <t>SEC-093</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #93)</t>
-  </si>
-  <si>
     <t>SEC-094</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #94)</t>
-  </si>
-  <si>
     <t>SEC-095</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #95)</t>
-  </si>
-  <si>
     <t>SEC-096</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #96)</t>
-  </si>
-  <si>
     <t>SEC-097</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #97)</t>
-  </si>
-  <si>
     <t>SEC-098</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #98)</t>
-  </si>
-  <si>
     <t>SEC-099</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #99)</t>
-  </si>
-  <si>
     <t>SEC-100</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #100)</t>
-  </si>
-  <si>
     <t>SEC-101</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #101)</t>
-  </si>
-  <si>
     <t>SEC-102</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #102)</t>
-  </si>
-  <si>
     <t>SEC-103</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #103)</t>
-  </si>
-  <si>
     <t>SEC-104</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #104)</t>
-  </si>
-  <si>
     <t>SEC-105</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #105)</t>
-  </si>
-  <si>
     <t>SEC-106</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #106)</t>
-  </si>
-  <si>
     <t>SEC-107</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #107)</t>
-  </si>
-  <si>
     <t>SEC-108</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #108)</t>
-  </si>
-  <si>
     <t>SEC-109</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #109)</t>
-  </si>
-  <si>
     <t>SEC-110</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #110)</t>
-  </si>
-  <si>
     <t>SEC-111</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #111)</t>
-  </si>
-  <si>
     <t>SEC-112</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #112)</t>
-  </si>
-  <si>
     <t>SEC-113</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #113)</t>
-  </si>
-  <si>
     <t>SEC-114</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #114)</t>
-  </si>
-  <si>
     <t>SEC-115</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #115)</t>
-  </si>
-  <si>
     <t>SEC-116</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #116)</t>
-  </si>
-  <si>
     <t>SEC-117</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #117)</t>
-  </si>
-  <si>
     <t>SEC-118</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #118)</t>
-  </si>
-  <si>
     <t>SEC-119</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #119)</t>
-  </si>
-  <si>
     <t>SEC-120</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #120)</t>
-  </si>
-  <si>
     <t>SEC-121</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #121)</t>
-  </si>
-  <si>
     <t>SEC-122</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #122)</t>
-  </si>
-  <si>
     <t>SEC-123</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #123)</t>
-  </si>
-  <si>
     <t>SEC-124</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #124)</t>
-  </si>
-  <si>
     <t>SEC-125</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #125)</t>
-  </si>
-  <si>
     <t>SEC-126</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #126)</t>
-  </si>
-  <si>
     <t>SEC-127</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #127)</t>
-  </si>
-  <si>
     <t>SEC-128</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #128)</t>
-  </si>
-  <si>
     <t>SEC-129</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #129)</t>
-  </si>
-  <si>
     <t>SEC-130</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #130)</t>
-  </si>
-  <si>
     <t>SEC-131</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #131)</t>
-  </si>
-  <si>
     <t>SEC-132</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #132)</t>
-  </si>
-  <si>
     <t>SEC-133</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #133)</t>
-  </si>
-  <si>
     <t>SEC-134</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #134)</t>
-  </si>
-  <si>
     <t>SEC-135</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #135)</t>
-  </si>
-  <si>
     <t>SEC-136</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #136)</t>
-  </si>
-  <si>
     <t>SEC-137</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #137)</t>
-  </si>
-  <si>
     <t>SEC-138</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #138)</t>
-  </si>
-  <si>
     <t>SEC-139</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #139)</t>
-  </si>
-  <si>
     <t>SEC-140</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #140)</t>
-  </si>
-  <si>
     <t>SEC-141</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #141)</t>
-  </si>
-  <si>
     <t>SEC-142</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #142)</t>
-  </si>
-  <si>
     <t>SEC-143</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #143)</t>
-  </si>
-  <si>
     <t>SEC-144</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #144)</t>
-  </si>
-  <si>
     <t>SEC-145</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #145)</t>
-  </si>
-  <si>
     <t>SEC-146</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #146)</t>
-  </si>
-  <si>
     <t>SEC-147</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #147)</t>
-  </si>
-  <si>
     <t>SEC-148</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #148)</t>
-  </si>
-  <si>
     <t>SEC-149</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #149)</t>
-  </si>
-  <si>
     <t>SEC-150</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #150)</t>
-  </si>
-  <si>
     <t>SEC-151</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #151)</t>
-  </si>
-  <si>
     <t>SEC-152</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #152)</t>
-  </si>
-  <si>
     <t>SEC-153</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #153)</t>
-  </si>
-  <si>
     <t>SEC-154</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #154)</t>
-  </si>
-  <si>
     <t>SEC-155</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #155)</t>
-  </si>
-  <si>
     <t>SEC-156</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #156)</t>
-  </si>
-  <si>
     <t>SEC-157</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #157)</t>
-  </si>
-  <si>
     <t>SEC-158</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #158)</t>
-  </si>
-  <si>
     <t>SEC-159</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #159)</t>
-  </si>
-  <si>
     <t>SEC-160</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #160)</t>
-  </si>
-  <si>
     <t>SEC-161</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #161)</t>
-  </si>
-  <si>
     <t>SEC-162</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #162)</t>
-  </si>
-  <si>
     <t>SEC-163</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #163)</t>
-  </si>
-  <si>
     <t>SEC-164</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #164)</t>
-  </si>
-  <si>
     <t>SEC-165</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #165)</t>
-  </si>
-  <si>
     <t>SEC-166</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #166)</t>
-  </si>
-  <si>
     <t>SEC-167</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #167)</t>
-  </si>
-  <si>
     <t>SEC-168</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #168)</t>
-  </si>
-  <si>
     <t>SEC-169</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #169)</t>
-  </si>
-  <si>
     <t>SEC-170</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #170)</t>
-  </si>
-  <si>
     <t>SEC-171</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #171)</t>
-  </si>
-  <si>
     <t>SEC-172</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #172)</t>
-  </si>
-  <si>
     <t>SEC-173</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #173)</t>
-  </si>
-  <si>
     <t>SEC-174</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #174)</t>
-  </si>
-  <si>
     <t>SEC-175</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #175)</t>
-  </si>
-  <si>
     <t>SEC-176</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #176)</t>
-  </si>
-  <si>
     <t>SEC-177</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #177)</t>
-  </si>
-  <si>
     <t>SEC-178</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #178)</t>
-  </si>
-  <si>
     <t>SEC-179</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #179)</t>
-  </si>
-  <si>
     <t>SEC-180</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #180)</t>
-  </si>
-  <si>
     <t>SEC-181</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #181)</t>
-  </si>
-  <si>
     <t>SEC-182</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #182)</t>
-  </si>
-  <si>
     <t>SEC-183</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #183)</t>
-  </si>
-  <si>
     <t>SEC-184</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #184)</t>
-  </si>
-  <si>
     <t>SEC-185</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #185)</t>
-  </si>
-  <si>
     <t>SEC-186</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #186)</t>
-  </si>
-  <si>
     <t>SEC-187</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #187)</t>
-  </si>
-  <si>
     <t>SEC-188</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #188)</t>
-  </si>
-  <si>
     <t>SEC-189</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #189)</t>
-  </si>
-  <si>
     <t>SEC-190</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #190)</t>
-  </si>
-  <si>
     <t>SEC-191</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #191)</t>
-  </si>
-  <si>
     <t>SEC-192</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #192)</t>
-  </si>
-  <si>
     <t>SEC-193</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #193)</t>
-  </si>
-  <si>
     <t>SEC-194</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #194)</t>
-  </si>
-  <si>
     <t>SEC-195</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #195)</t>
-  </si>
-  <si>
     <t>SEC-196</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #196)</t>
-  </si>
-  <si>
     <t>SEC-197</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #197)</t>
-  </si>
-  <si>
     <t>SEC-198</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #198)</t>
-  </si>
-  <si>
     <t>SEC-199</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #199)</t>
-  </si>
-  <si>
     <t>SEC-200</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #200)</t>
-  </si>
-  <si>
     <t>SEC-201</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #201)</t>
-  </si>
-  <si>
     <t>SEC-202</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #202)</t>
-  </si>
-  <si>
     <t>SEC-203</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #203)</t>
-  </si>
-  <si>
     <t>SEC-204</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #204)</t>
-  </si>
-  <si>
     <t>SEC-205</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #205)</t>
-  </si>
-  <si>
     <t>SEC-206</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #206)</t>
-  </si>
-  <si>
     <t>SEC-207</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #207)</t>
-  </si>
-  <si>
     <t>SEC-208</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #208)</t>
-  </si>
-  <si>
     <t>SEC-209</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #209)</t>
-  </si>
-  <si>
     <t>SEC-210</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #210)</t>
-  </si>
-  <si>
     <t>SEC-211</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #211)</t>
-  </si>
-  <si>
     <t>SEC-212</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #212)</t>
-  </si>
-  <si>
     <t>SEC-213</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #213)</t>
-  </si>
-  <si>
     <t>SEC-214</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #214)</t>
-  </si>
-  <si>
     <t>SEC-215</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #215)</t>
-  </si>
-  <si>
     <t>SEC-216</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #216)</t>
-  </si>
-  <si>
     <t>SEC-217</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #217)</t>
-  </si>
-  <si>
     <t>SEC-218</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #218)</t>
-  </si>
-  <si>
     <t>SEC-219</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #219)</t>
-  </si>
-  <si>
     <t>SEC-220</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #220)</t>
-  </si>
-  <si>
     <t>SEC-221</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #221)</t>
-  </si>
-  <si>
     <t>SEC-222</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #222)</t>
-  </si>
-  <si>
     <t>SEC-223</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #223)</t>
-  </si>
-  <si>
     <t>SEC-224</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #224)</t>
-  </si>
-  <si>
     <t>SEC-225</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #225)</t>
-  </si>
-  <si>
     <t>SEC-226</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #226)</t>
-  </si>
-  <si>
     <t>SEC-227</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #227)</t>
-  </si>
-  <si>
     <t>SEC-228</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #228)</t>
-  </si>
-  <si>
     <t>SEC-229</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #229)</t>
-  </si>
-  <si>
     <t>SEC-230</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #230)</t>
-  </si>
-  <si>
     <t>SEC-231</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #231)</t>
-  </si>
-  <si>
     <t>SEC-232</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #232)</t>
-  </si>
-  <si>
     <t>SEC-233</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #233)</t>
-  </si>
-  <si>
     <t>SEC-234</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #234)</t>
-  </si>
-  <si>
     <t>SEC-235</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #235)</t>
-  </si>
-  <si>
     <t>SEC-236</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #236)</t>
-  </si>
-  <si>
     <t>SEC-237</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #237)</t>
-  </si>
-  <si>
     <t>SEC-238</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #238)</t>
-  </si>
-  <si>
     <t>SEC-239</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #239)</t>
-  </si>
-  <si>
     <t>SEC-240</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #240)</t>
-  </si>
-  <si>
     <t>SEC-241</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #241)</t>
-  </si>
-  <si>
     <t>SEC-242</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #242)</t>
-  </si>
-  <si>
     <t>SEC-243</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #243)</t>
-  </si>
-  <si>
     <t>SEC-244</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #244)</t>
-  </si>
-  <si>
     <t>SEC-245</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #245)</t>
-  </si>
-  <si>
     <t>SEC-246</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #246)</t>
-  </si>
-  <si>
     <t>SEC-247</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #247)</t>
-  </si>
-  <si>
     <t>SEC-248</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #248)</t>
-  </si>
-  <si>
     <t>SEC-249</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #249)</t>
-  </si>
-  <si>
     <t>SEC-250</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #250)</t>
-  </si>
-  <si>
     <t>SEC-251</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #251)</t>
-  </si>
-  <si>
     <t>SEC-252</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #252)</t>
-  </si>
-  <si>
     <t>SEC-253</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #253)</t>
-  </si>
-  <si>
     <t>SEC-254</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #254)</t>
-  </si>
-  <si>
     <t>SEC-255</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #255)</t>
-  </si>
-  <si>
     <t>SEC-256</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #256)</t>
-  </si>
-  <si>
     <t>SEC-257</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #257)</t>
-  </si>
-  <si>
     <t>SEC-258</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #258)</t>
-  </si>
-  <si>
     <t>SEC-259</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #259)</t>
-  </si>
-  <si>
     <t>SEC-260</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #260)</t>
-  </si>
-  <si>
     <t>SEC-261</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #261)</t>
-  </si>
-  <si>
     <t>SEC-262</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #262)</t>
-  </si>
-  <si>
     <t>SEC-263</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #263)</t>
-  </si>
-  <si>
     <t>SEC-264</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #264)</t>
-  </si>
-  <si>
     <t>SEC-265</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #265)</t>
-  </si>
-  <si>
     <t>SEC-266</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #266)</t>
-  </si>
-  <si>
     <t>SEC-267</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #267)</t>
-  </si>
-  <si>
     <t>SEC-268</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #268)</t>
-  </si>
-  <si>
     <t>SEC-269</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #269)</t>
-  </si>
-  <si>
     <t>SEC-270</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #270)</t>
-  </si>
-  <si>
     <t>SEC-271</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #271)</t>
-  </si>
-  <si>
     <t>SEC-272</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #272)</t>
-  </si>
-  <si>
     <t>SEC-273</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #273)</t>
-  </si>
-  <si>
     <t>SEC-274</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #274)</t>
-  </si>
-  <si>
     <t>SEC-275</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #275)</t>
-  </si>
-  <si>
     <t>SEC-276</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #276)</t>
-  </si>
-  <si>
     <t>SEC-277</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #277)</t>
-  </si>
-  <si>
     <t>SEC-278</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #278)</t>
-  </si>
-  <si>
     <t>SEC-279</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #279)</t>
-  </si>
-  <si>
     <t>SEC-280</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #280)</t>
-  </si>
-  <si>
     <t>SEC-281</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #281)</t>
-  </si>
-  <si>
     <t>SEC-282</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #282)</t>
-  </si>
-  <si>
     <t>SEC-283</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #283)</t>
-  </si>
-  <si>
     <t>SEC-284</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #284)</t>
-  </si>
-  <si>
     <t>SEC-285</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #285)</t>
-  </si>
-  <si>
     <t>SEC-286</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #286)</t>
-  </si>
-  <si>
     <t>SEC-287</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #287)</t>
-  </si>
-  <si>
     <t>SEC-288</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #288)</t>
-  </si>
-  <si>
     <t>SEC-289</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #289)</t>
-  </si>
-  <si>
     <t>SEC-290</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #290)</t>
-  </si>
-  <si>
     <t>SEC-291</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #291)</t>
-  </si>
-  <si>
     <t>SEC-292</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #292)</t>
-  </si>
-  <si>
     <t>SEC-293</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #293)</t>
-  </si>
-  <si>
     <t>SEC-294</t>
   </si>
   <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #294)</t>
-  </si>
-  <si>
     <t>SEC-295</t>
   </si>
   <si>
-    <t>Verified no live secret keys or credentials in commit history (Check #295)</t>
-  </si>
-  <si>
     <t>SEC-296</t>
   </si>
   <si>
-    <t>Frontend dependencies verified for CVE security advisories (Check #296)</t>
-  </si>
-  <si>
     <t>SEC-297</t>
   </si>
   <si>
-    <t>Static analysis check for OWASP Top 10 security risks (Check #297)</t>
-  </si>
-  <si>
     <t>SEC-298</t>
   </si>
   <si>
-    <t>Filesystem scan for signature-based threat detection (Check #298)</t>
-  </si>
-  <si>
     <t>SEC-299</t>
   </si>
   <si>
-    <t>Python packages compatibility and vulnerability audit (Check #299)</t>
-  </si>
-  <si>
     <t>SEC-300</t>
-  </si>
-  <si>
-    <t>Input validation sanitizer rule configuration compliance (Check #300)</t>
   </si>
 </sst>
 </file>
@@ -3412,7 +2680,7 @@
         <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
@@ -3420,7 +2688,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B59" t="s">
         <v>21</v>
@@ -3432,7 +2700,7 @@
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
@@ -3440,7 +2708,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B60" t="s">
         <v>25</v>
@@ -3452,7 +2720,7 @@
         <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
@@ -3460,7 +2728,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B61" t="s">
         <v>29</v>
@@ -3472,7 +2740,7 @@
         <v>30</v>
       </c>
       <c r="E61" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
@@ -3480,7 +2748,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
@@ -3492,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
@@ -3500,7 +2768,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3512,7 +2780,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
@@ -3520,7 +2788,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3532,7 +2800,7 @@
         <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="F64" t="s">
         <v>11</v>
@@ -3540,7 +2808,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
         <v>21</v>
@@ -3552,7 +2820,7 @@
         <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
@@ -3560,7 +2828,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
         <v>25</v>
@@ -3572,7 +2840,7 @@
         <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>149</v>
+        <v>37</v>
       </c>
       <c r="F66" t="s">
         <v>11</v>
@@ -3580,7 +2848,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s">
         <v>29</v>
@@ -3592,7 +2860,7 @@
         <v>30</v>
       </c>
       <c r="E67" t="s">
-        <v>151</v>
+        <v>39</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
@@ -3600,7 +2868,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
@@ -3612,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="F68" t="s">
         <v>11</v>
@@ -3620,7 +2888,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -3632,7 +2900,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>155</v>
+        <v>43</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
@@ -3640,7 +2908,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -3652,7 +2920,7 @@
         <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="F70" t="s">
         <v>11</v>
@@ -3660,7 +2928,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B71" t="s">
         <v>21</v>
@@ -3672,7 +2940,7 @@
         <v>22</v>
       </c>
       <c r="E71" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="F71" t="s">
         <v>11</v>
@@ -3680,7 +2948,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B72" t="s">
         <v>25</v>
@@ -3692,7 +2960,7 @@
         <v>26</v>
       </c>
       <c r="E72" t="s">
-        <v>161</v>
+        <v>49</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
@@ -3700,7 +2968,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B73" t="s">
         <v>29</v>
@@ -3712,7 +2980,7 @@
         <v>30</v>
       </c>
       <c r="E73" t="s">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
@@ -3720,7 +2988,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
@@ -3732,7 +3000,7 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="F74" t="s">
         <v>11</v>
@@ -3740,7 +3008,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -3752,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s">
         <v>11</v>
@@ -3760,7 +3028,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -3772,7 +3040,7 @@
         <v>18</v>
       </c>
       <c r="E76" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="F76" t="s">
         <v>11</v>
@@ -3780,7 +3048,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="B77" t="s">
         <v>21</v>
@@ -3792,7 +3060,7 @@
         <v>22</v>
       </c>
       <c r="E77" t="s">
-        <v>171</v>
+        <v>59</v>
       </c>
       <c r="F77" t="s">
         <v>11</v>
@@ -3800,7 +3068,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B78" t="s">
         <v>25</v>
@@ -3812,7 +3080,7 @@
         <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="F78" t="s">
         <v>11</v>
@@ -3820,7 +3088,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B79" t="s">
         <v>29</v>
@@ -3832,7 +3100,7 @@
         <v>30</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="F79" t="s">
         <v>11</v>
@@ -3840,7 +3108,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="B80" t="s">
         <v>7</v>
@@ -3852,7 +3120,7 @@
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="F80" t="s">
         <v>11</v>
@@ -3860,7 +3128,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -3872,7 +3140,7 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="F81" t="s">
         <v>11</v>
@@ -3880,7 +3148,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -3892,7 +3160,7 @@
         <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="F82" t="s">
         <v>11</v>
@@ -3900,7 +3168,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="B83" t="s">
         <v>21</v>
@@ -3912,7 +3180,7 @@
         <v>22</v>
       </c>
       <c r="E83" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="F83" t="s">
         <v>11</v>
@@ -3920,7 +3188,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B84" t="s">
         <v>25</v>
@@ -3932,7 +3200,7 @@
         <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="F84" t="s">
         <v>11</v>
@@ -3940,7 +3208,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="B85" t="s">
         <v>29</v>
@@ -3952,7 +3220,7 @@
         <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="F85" t="s">
         <v>11</v>
@@ -3960,7 +3228,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="B86" t="s">
         <v>7</v>
@@ -3972,7 +3240,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="F86" t="s">
         <v>11</v>
@@ -3980,7 +3248,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -3992,7 +3260,7 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="F87" t="s">
         <v>11</v>
@@ -4000,7 +3268,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -4012,7 +3280,7 @@
         <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="F88" t="s">
         <v>11</v>
@@ -4020,7 +3288,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="B89" t="s">
         <v>21</v>
@@ -4032,7 +3300,7 @@
         <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="F89" t="s">
         <v>11</v>
@@ -4040,7 +3308,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="B90" t="s">
         <v>25</v>
@@ -4052,7 +3320,7 @@
         <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>197</v>
+        <v>85</v>
       </c>
       <c r="F90" t="s">
         <v>11</v>
@@ -4060,7 +3328,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B91" t="s">
         <v>29</v>
@@ -4072,7 +3340,7 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>199</v>
+        <v>87</v>
       </c>
       <c r="F91" t="s">
         <v>11</v>
@@ -4080,7 +3348,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="B92" t="s">
         <v>7</v>
@@ -4092,7 +3360,7 @@
         <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>201</v>
+        <v>89</v>
       </c>
       <c r="F92" t="s">
         <v>11</v>
@@ -4100,7 +3368,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -4112,7 +3380,7 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
       <c r="F93" t="s">
         <v>11</v>
@@ -4120,7 +3388,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -4132,7 +3400,7 @@
         <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>205</v>
+        <v>93</v>
       </c>
       <c r="F94" t="s">
         <v>11</v>
@@ -4140,7 +3408,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="B95" t="s">
         <v>21</v>
@@ -4152,7 +3420,7 @@
         <v>22</v>
       </c>
       <c r="E95" t="s">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="F95" t="s">
         <v>11</v>
@@ -4160,7 +3428,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="B96" t="s">
         <v>25</v>
@@ -4172,7 +3440,7 @@
         <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>209</v>
+        <v>97</v>
       </c>
       <c r="F96" t="s">
         <v>11</v>
@@ -4180,7 +3448,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="B97" t="s">
         <v>29</v>
@@ -4192,7 +3460,7 @@
         <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="F97" t="s">
         <v>11</v>
@@ -4200,7 +3468,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="B98" t="s">
         <v>7</v>
@@ -4212,7 +3480,7 @@
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="F98" t="s">
         <v>11</v>
@@ -4220,7 +3488,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -4232,7 +3500,7 @@
         <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>215</v>
+        <v>103</v>
       </c>
       <c r="F99" t="s">
         <v>11</v>
@@ -4240,7 +3508,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -4252,7 +3520,7 @@
         <v>18</v>
       </c>
       <c r="E100" t="s">
-        <v>217</v>
+        <v>105</v>
       </c>
       <c r="F100" t="s">
         <v>11</v>
@@ -4260,7 +3528,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
@@ -4272,7 +3540,7 @@
         <v>22</v>
       </c>
       <c r="E101" t="s">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="F101" t="s">
         <v>11</v>
@@ -4280,7 +3548,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="B102" t="s">
         <v>25</v>
@@ -4292,7 +3560,7 @@
         <v>26</v>
       </c>
       <c r="E102" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="F102" t="s">
         <v>11</v>
@@ -4300,7 +3568,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="B103" t="s">
         <v>29</v>
@@ -4312,7 +3580,7 @@
         <v>30</v>
       </c>
       <c r="E103" t="s">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -4320,7 +3588,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
       <c r="B104" t="s">
         <v>7</v>
@@ -4332,7 +3600,7 @@
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="F104" t="s">
         <v>11</v>
@@ -4340,7 +3608,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -4352,7 +3620,7 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="F105" t="s">
         <v>11</v>
@@ -4360,7 +3628,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -4372,7 +3640,7 @@
         <v>18</v>
       </c>
       <c r="E106" t="s">
-        <v>229</v>
+        <v>117</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
@@ -4380,7 +3648,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="B107" t="s">
         <v>21</v>
@@ -4392,7 +3660,7 @@
         <v>22</v>
       </c>
       <c r="E107" t="s">
-        <v>231</v>
+        <v>119</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
@@ -4400,7 +3668,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="B108" t="s">
         <v>25</v>
@@ -4412,7 +3680,7 @@
         <v>26</v>
       </c>
       <c r="E108" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
       <c r="F108" t="s">
         <v>11</v>
@@ -4420,7 +3688,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B109" t="s">
         <v>29</v>
@@ -4432,7 +3700,7 @@
         <v>30</v>
       </c>
       <c r="E109" t="s">
-        <v>235</v>
+        <v>123</v>
       </c>
       <c r="F109" t="s">
         <v>11</v>
@@ -4440,7 +3708,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
@@ -4452,7 +3720,7 @@
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>237</v>
+        <v>125</v>
       </c>
       <c r="F110" t="s">
         <v>11</v>
@@ -4460,7 +3728,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>238</v>
+        <v>185</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -4472,7 +3740,7 @@
         <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>239</v>
+        <v>127</v>
       </c>
       <c r="F111" t="s">
         <v>11</v>
@@ -4480,7 +3748,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>240</v>
+        <v>186</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -4492,7 +3760,7 @@
         <v>18</v>
       </c>
       <c r="E112" t="s">
-        <v>241</v>
+        <v>129</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -4500,7 +3768,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="B113" t="s">
         <v>21</v>
@@ -4512,7 +3780,7 @@
         <v>22</v>
       </c>
       <c r="E113" t="s">
-        <v>243</v>
+        <v>131</v>
       </c>
       <c r="F113" t="s">
         <v>11</v>
@@ -4520,7 +3788,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="B114" t="s">
         <v>25</v>
@@ -4532,7 +3800,7 @@
         <v>26</v>
       </c>
       <c r="E114" t="s">
-        <v>245</v>
+        <v>10</v>
       </c>
       <c r="F114" t="s">
         <v>11</v>
@@ -4540,7 +3808,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="B115" t="s">
         <v>29</v>
@@ -4552,7 +3820,7 @@
         <v>30</v>
       </c>
       <c r="E115" t="s">
-        <v>247</v>
+        <v>15</v>
       </c>
       <c r="F115" t="s">
         <v>11</v>
@@ -4560,7 +3828,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>248</v>
+        <v>190</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
@@ -4572,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="F116" t="s">
         <v>11</v>
@@ -4580,7 +3848,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
@@ -4592,7 +3860,7 @@
         <v>14</v>
       </c>
       <c r="E117" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
@@ -4600,7 +3868,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>252</v>
+        <v>192</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
@@ -4612,7 +3880,7 @@
         <v>18</v>
       </c>
       <c r="E118" t="s">
-        <v>253</v>
+        <v>27</v>
       </c>
       <c r="F118" t="s">
         <v>11</v>
@@ -4620,7 +3888,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="B119" t="s">
         <v>21</v>
@@ -4632,7 +3900,7 @@
         <v>22</v>
       </c>
       <c r="E119" t="s">
-        <v>255</v>
+        <v>31</v>
       </c>
       <c r="F119" t="s">
         <v>11</v>
@@ -4640,7 +3908,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="B120" t="s">
         <v>25</v>
@@ -4652,7 +3920,7 @@
         <v>26</v>
       </c>
       <c r="E120" t="s">
-        <v>257</v>
+        <v>33</v>
       </c>
       <c r="F120" t="s">
         <v>11</v>
@@ -4660,7 +3928,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>258</v>
+        <v>195</v>
       </c>
       <c r="B121" t="s">
         <v>29</v>
@@ -4672,7 +3940,7 @@
         <v>30</v>
       </c>
       <c r="E121" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="F121" t="s">
         <v>11</v>
@@ -4680,7 +3948,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
@@ -4692,7 +3960,7 @@
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="F122" t="s">
         <v>11</v>
@@ -4700,7 +3968,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
@@ -4712,7 +3980,7 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="F123" t="s">
         <v>11</v>
@@ -4720,7 +3988,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
@@ -4732,7 +4000,7 @@
         <v>18</v>
       </c>
       <c r="E124" t="s">
-        <v>265</v>
+        <v>41</v>
       </c>
       <c r="F124" t="s">
         <v>11</v>
@@ -4740,7 +4008,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="B125" t="s">
         <v>21</v>
@@ -4752,7 +4020,7 @@
         <v>22</v>
       </c>
       <c r="E125" t="s">
-        <v>267</v>
+        <v>43</v>
       </c>
       <c r="F125" t="s">
         <v>11</v>
@@ -4760,7 +4028,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="B126" t="s">
         <v>25</v>
@@ -4772,7 +4040,7 @@
         <v>26</v>
       </c>
       <c r="E126" t="s">
-        <v>269</v>
+        <v>45</v>
       </c>
       <c r="F126" t="s">
         <v>11</v>
@@ -4780,7 +4048,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>270</v>
+        <v>201</v>
       </c>
       <c r="B127" t="s">
         <v>29</v>
@@ -4792,7 +4060,7 @@
         <v>30</v>
       </c>
       <c r="E127" t="s">
-        <v>271</v>
+        <v>47</v>
       </c>
       <c r="F127" t="s">
         <v>11</v>
@@ -4800,7 +4068,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>272</v>
+        <v>202</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
@@ -4812,7 +4080,7 @@
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>273</v>
+        <v>49</v>
       </c>
       <c r="F128" t="s">
         <v>11</v>
@@ -4820,7 +4088,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>274</v>
+        <v>203</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
@@ -4832,7 +4100,7 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>275</v>
+        <v>51</v>
       </c>
       <c r="F129" t="s">
         <v>11</v>
@@ -4840,7 +4108,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="B130" t="s">
         <v>17</v>
@@ -4852,7 +4120,7 @@
         <v>18</v>
       </c>
       <c r="E130" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="F130" t="s">
         <v>11</v>
@@ -4860,7 +4128,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>278</v>
+        <v>205</v>
       </c>
       <c r="B131" t="s">
         <v>21</v>
@@ -4872,7 +4140,7 @@
         <v>22</v>
       </c>
       <c r="E131" t="s">
-        <v>279</v>
+        <v>55</v>
       </c>
       <c r="F131" t="s">
         <v>11</v>
@@ -4880,7 +4148,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="B132" t="s">
         <v>25</v>
@@ -4892,7 +4160,7 @@
         <v>26</v>
       </c>
       <c r="E132" t="s">
-        <v>281</v>
+        <v>57</v>
       </c>
       <c r="F132" t="s">
         <v>11</v>
@@ -4900,7 +4168,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>282</v>
+        <v>207</v>
       </c>
       <c r="B133" t="s">
         <v>29</v>
@@ -4912,7 +4180,7 @@
         <v>30</v>
       </c>
       <c r="E133" t="s">
-        <v>283</v>
+        <v>59</v>
       </c>
       <c r="F133" t="s">
         <v>11</v>
@@ -4920,7 +4188,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
@@ -4932,7 +4200,7 @@
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>285</v>
+        <v>61</v>
       </c>
       <c r="F134" t="s">
         <v>11</v>
@@ -4940,7 +4208,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>286</v>
+        <v>209</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
@@ -4952,7 +4220,7 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>287</v>
+        <v>63</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -4960,7 +4228,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>288</v>
+        <v>210</v>
       </c>
       <c r="B136" t="s">
         <v>17</v>
@@ -4972,7 +4240,7 @@
         <v>18</v>
       </c>
       <c r="E136" t="s">
-        <v>289</v>
+        <v>65</v>
       </c>
       <c r="F136" t="s">
         <v>11</v>
@@ -4980,7 +4248,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>290</v>
+        <v>211</v>
       </c>
       <c r="B137" t="s">
         <v>21</v>
@@ -4992,7 +4260,7 @@
         <v>22</v>
       </c>
       <c r="E137" t="s">
-        <v>291</v>
+        <v>67</v>
       </c>
       <c r="F137" t="s">
         <v>11</v>
@@ -5000,7 +4268,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="B138" t="s">
         <v>25</v>
@@ -5012,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="E138" t="s">
-        <v>293</v>
+        <v>69</v>
       </c>
       <c r="F138" t="s">
         <v>11</v>
@@ -5020,7 +4288,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>294</v>
+        <v>213</v>
       </c>
       <c r="B139" t="s">
         <v>29</v>
@@ -5032,7 +4300,7 @@
         <v>30</v>
       </c>
       <c r="E139" t="s">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="F139" t="s">
         <v>11</v>
@@ -5040,7 +4308,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>296</v>
+        <v>214</v>
       </c>
       <c r="B140" t="s">
         <v>7</v>
@@ -5052,7 +4320,7 @@
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>297</v>
+        <v>73</v>
       </c>
       <c r="F140" t="s">
         <v>11</v>
@@ -5060,7 +4328,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>298</v>
+        <v>215</v>
       </c>
       <c r="B141" t="s">
         <v>13</v>
@@ -5072,7 +4340,7 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>299</v>
+        <v>75</v>
       </c>
       <c r="F141" t="s">
         <v>11</v>
@@ -5080,7 +4348,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>300</v>
+        <v>216</v>
       </c>
       <c r="B142" t="s">
         <v>17</v>
@@ -5092,7 +4360,7 @@
         <v>18</v>
       </c>
       <c r="E142" t="s">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="F142" t="s">
         <v>11</v>
@@ -5100,7 +4368,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>302</v>
+        <v>217</v>
       </c>
       <c r="B143" t="s">
         <v>21</v>
@@ -5112,7 +4380,7 @@
         <v>22</v>
       </c>
       <c r="E143" t="s">
-        <v>303</v>
+        <v>79</v>
       </c>
       <c r="F143" t="s">
         <v>11</v>
@@ -5120,7 +4388,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>304</v>
+        <v>218</v>
       </c>
       <c r="B144" t="s">
         <v>25</v>
@@ -5132,7 +4400,7 @@
         <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="F144" t="s">
         <v>11</v>
@@ -5140,7 +4408,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>306</v>
+        <v>219</v>
       </c>
       <c r="B145" t="s">
         <v>29</v>
@@ -5152,7 +4420,7 @@
         <v>30</v>
       </c>
       <c r="E145" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="F145" t="s">
         <v>11</v>
@@ -5160,7 +4428,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>308</v>
+        <v>220</v>
       </c>
       <c r="B146" t="s">
         <v>7</v>
@@ -5172,7 +4440,7 @@
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="F146" t="s">
         <v>11</v>
@@ -5180,7 +4448,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>310</v>
+        <v>221</v>
       </c>
       <c r="B147" t="s">
         <v>13</v>
@@ -5192,7 +4460,7 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>311</v>
+        <v>87</v>
       </c>
       <c r="F147" t="s">
         <v>11</v>
@@ -5200,7 +4468,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>312</v>
+        <v>222</v>
       </c>
       <c r="B148" t="s">
         <v>17</v>
@@ -5212,7 +4480,7 @@
         <v>18</v>
       </c>
       <c r="E148" t="s">
-        <v>313</v>
+        <v>89</v>
       </c>
       <c r="F148" t="s">
         <v>11</v>
@@ -5220,7 +4488,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>314</v>
+        <v>223</v>
       </c>
       <c r="B149" t="s">
         <v>21</v>
@@ -5232,7 +4500,7 @@
         <v>22</v>
       </c>
       <c r="E149" t="s">
-        <v>315</v>
+        <v>91</v>
       </c>
       <c r="F149" t="s">
         <v>11</v>
@@ -5240,7 +4508,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>316</v>
+        <v>224</v>
       </c>
       <c r="B150" t="s">
         <v>25</v>
@@ -5252,7 +4520,7 @@
         <v>26</v>
       </c>
       <c r="E150" t="s">
-        <v>317</v>
+        <v>93</v>
       </c>
       <c r="F150" t="s">
         <v>11</v>
@@ -5260,7 +4528,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>318</v>
+        <v>225</v>
       </c>
       <c r="B151" t="s">
         <v>29</v>
@@ -5272,7 +4540,7 @@
         <v>30</v>
       </c>
       <c r="E151" t="s">
-        <v>319</v>
+        <v>95</v>
       </c>
       <c r="F151" t="s">
         <v>11</v>
@@ -5280,7 +4548,7 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>320</v>
+        <v>226</v>
       </c>
       <c r="B152" t="s">
         <v>7</v>
@@ -5292,7 +4560,7 @@
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>321</v>
+        <v>97</v>
       </c>
       <c r="F152" t="s">
         <v>11</v>
@@ -5300,7 +4568,7 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>322</v>
+        <v>227</v>
       </c>
       <c r="B153" t="s">
         <v>13</v>
@@ -5312,7 +4580,7 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>323</v>
+        <v>99</v>
       </c>
       <c r="F153" t="s">
         <v>11</v>
@@ -5320,7 +4588,7 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>324</v>
+        <v>228</v>
       </c>
       <c r="B154" t="s">
         <v>17</v>
@@ -5332,7 +4600,7 @@
         <v>18</v>
       </c>
       <c r="E154" t="s">
-        <v>325</v>
+        <v>101</v>
       </c>
       <c r="F154" t="s">
         <v>11</v>
@@ -5340,7 +4608,7 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="B155" t="s">
         <v>21</v>
@@ -5352,7 +4620,7 @@
         <v>22</v>
       </c>
       <c r="E155" t="s">
-        <v>327</v>
+        <v>103</v>
       </c>
       <c r="F155" t="s">
         <v>11</v>
@@ -5360,7 +4628,7 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>328</v>
+        <v>230</v>
       </c>
       <c r="B156" t="s">
         <v>25</v>
@@ -5372,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="E156" t="s">
-        <v>329</v>
+        <v>105</v>
       </c>
       <c r="F156" t="s">
         <v>11</v>
@@ -5380,7 +4648,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>330</v>
+        <v>231</v>
       </c>
       <c r="B157" t="s">
         <v>29</v>
@@ -5392,7 +4660,7 @@
         <v>30</v>
       </c>
       <c r="E157" t="s">
-        <v>331</v>
+        <v>107</v>
       </c>
       <c r="F157" t="s">
         <v>11</v>
@@ -5400,7 +4668,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>332</v>
+        <v>232</v>
       </c>
       <c r="B158" t="s">
         <v>7</v>
@@ -5412,7 +4680,7 @@
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>333</v>
+        <v>109</v>
       </c>
       <c r="F158" t="s">
         <v>11</v>
@@ -5420,7 +4688,7 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>334</v>
+        <v>233</v>
       </c>
       <c r="B159" t="s">
         <v>13</v>
@@ -5432,7 +4700,7 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>335</v>
+        <v>111</v>
       </c>
       <c r="F159" t="s">
         <v>11</v>
@@ -5440,7 +4708,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>336</v>
+        <v>234</v>
       </c>
       <c r="B160" t="s">
         <v>17</v>
@@ -5452,7 +4720,7 @@
         <v>18</v>
       </c>
       <c r="E160" t="s">
-        <v>337</v>
+        <v>113</v>
       </c>
       <c r="F160" t="s">
         <v>11</v>
@@ -5460,7 +4728,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>338</v>
+        <v>235</v>
       </c>
       <c r="B161" t="s">
         <v>21</v>
@@ -5472,7 +4740,7 @@
         <v>22</v>
       </c>
       <c r="E161" t="s">
-        <v>339</v>
+        <v>115</v>
       </c>
       <c r="F161" t="s">
         <v>11</v>
@@ -5480,7 +4748,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>340</v>
+        <v>236</v>
       </c>
       <c r="B162" t="s">
         <v>25</v>
@@ -5492,7 +4760,7 @@
         <v>26</v>
       </c>
       <c r="E162" t="s">
-        <v>341</v>
+        <v>117</v>
       </c>
       <c r="F162" t="s">
         <v>11</v>
@@ -5500,7 +4768,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>342</v>
+        <v>237</v>
       </c>
       <c r="B163" t="s">
         <v>29</v>
@@ -5512,7 +4780,7 @@
         <v>30</v>
       </c>
       <c r="E163" t="s">
-        <v>343</v>
+        <v>119</v>
       </c>
       <c r="F163" t="s">
         <v>11</v>
@@ -5520,7 +4788,7 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>344</v>
+        <v>238</v>
       </c>
       <c r="B164" t="s">
         <v>7</v>
@@ -5532,7 +4800,7 @@
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>345</v>
+        <v>121</v>
       </c>
       <c r="F164" t="s">
         <v>11</v>
@@ -5540,7 +4808,7 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>346</v>
+        <v>239</v>
       </c>
       <c r="B165" t="s">
         <v>13</v>
@@ -5552,7 +4820,7 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>347</v>
+        <v>123</v>
       </c>
       <c r="F165" t="s">
         <v>11</v>
@@ -5560,7 +4828,7 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>348</v>
+        <v>240</v>
       </c>
       <c r="B166" t="s">
         <v>17</v>
@@ -5572,7 +4840,7 @@
         <v>18</v>
       </c>
       <c r="E166" t="s">
-        <v>349</v>
+        <v>125</v>
       </c>
       <c r="F166" t="s">
         <v>11</v>
@@ -5580,7 +4848,7 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>350</v>
+        <v>241</v>
       </c>
       <c r="B167" t="s">
         <v>21</v>
@@ -5592,7 +4860,7 @@
         <v>22</v>
       </c>
       <c r="E167" t="s">
-        <v>351</v>
+        <v>127</v>
       </c>
       <c r="F167" t="s">
         <v>11</v>
@@ -5600,7 +4868,7 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>352</v>
+        <v>242</v>
       </c>
       <c r="B168" t="s">
         <v>25</v>
@@ -5612,7 +4880,7 @@
         <v>26</v>
       </c>
       <c r="E168" t="s">
-        <v>353</v>
+        <v>129</v>
       </c>
       <c r="F168" t="s">
         <v>11</v>
@@ -5620,7 +4888,7 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>354</v>
+        <v>243</v>
       </c>
       <c r="B169" t="s">
         <v>29</v>
@@ -5632,7 +4900,7 @@
         <v>30</v>
       </c>
       <c r="E169" t="s">
-        <v>355</v>
+        <v>131</v>
       </c>
       <c r="F169" t="s">
         <v>11</v>
@@ -5640,7 +4908,7 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
@@ -5652,7 +4920,7 @@
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="F170" t="s">
         <v>11</v>
@@ -5660,7 +4928,7 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>358</v>
+        <v>245</v>
       </c>
       <c r="B171" t="s">
         <v>13</v>
@@ -5672,7 +4940,7 @@
         <v>14</v>
       </c>
       <c r="E171" t="s">
-        <v>359</v>
+        <v>15</v>
       </c>
       <c r="F171" t="s">
         <v>11</v>
@@ -5680,7 +4948,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>360</v>
+        <v>246</v>
       </c>
       <c r="B172" t="s">
         <v>17</v>
@@ -5692,7 +4960,7 @@
         <v>18</v>
       </c>
       <c r="E172" t="s">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="F172" t="s">
         <v>11</v>
@@ -5700,7 +4968,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>362</v>
+        <v>247</v>
       </c>
       <c r="B173" t="s">
         <v>21</v>
@@ -5712,7 +4980,7 @@
         <v>22</v>
       </c>
       <c r="E173" t="s">
-        <v>363</v>
+        <v>23</v>
       </c>
       <c r="F173" t="s">
         <v>11</v>
@@ -5720,7 +4988,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>364</v>
+        <v>248</v>
       </c>
       <c r="B174" t="s">
         <v>25</v>
@@ -5732,7 +5000,7 @@
         <v>26</v>
       </c>
       <c r="E174" t="s">
-        <v>365</v>
+        <v>27</v>
       </c>
       <c r="F174" t="s">
         <v>11</v>
@@ -5740,7 +5008,7 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>366</v>
+        <v>249</v>
       </c>
       <c r="B175" t="s">
         <v>29</v>
@@ -5752,7 +5020,7 @@
         <v>30</v>
       </c>
       <c r="E175" t="s">
-        <v>367</v>
+        <v>31</v>
       </c>
       <c r="F175" t="s">
         <v>11</v>
@@ -5760,7 +5028,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>368</v>
+        <v>250</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
@@ -5772,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>369</v>
+        <v>33</v>
       </c>
       <c r="F176" t="s">
         <v>11</v>
@@ -5780,7 +5048,7 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>370</v>
+        <v>251</v>
       </c>
       <c r="B177" t="s">
         <v>13</v>
@@ -5792,7 +5060,7 @@
         <v>14</v>
       </c>
       <c r="E177" t="s">
-        <v>371</v>
+        <v>35</v>
       </c>
       <c r="F177" t="s">
         <v>11</v>
@@ -5800,7 +5068,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>372</v>
+        <v>252</v>
       </c>
       <c r="B178" t="s">
         <v>17</v>
@@ -5812,7 +5080,7 @@
         <v>18</v>
       </c>
       <c r="E178" t="s">
-        <v>373</v>
+        <v>37</v>
       </c>
       <c r="F178" t="s">
         <v>11</v>
@@ -5820,7 +5088,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>374</v>
+        <v>253</v>
       </c>
       <c r="B179" t="s">
         <v>21</v>
@@ -5832,7 +5100,7 @@
         <v>22</v>
       </c>
       <c r="E179" t="s">
-        <v>375</v>
+        <v>39</v>
       </c>
       <c r="F179" t="s">
         <v>11</v>
@@ -5840,7 +5108,7 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>376</v>
+        <v>254</v>
       </c>
       <c r="B180" t="s">
         <v>25</v>
@@ -5852,7 +5120,7 @@
         <v>26</v>
       </c>
       <c r="E180" t="s">
-        <v>377</v>
+        <v>41</v>
       </c>
       <c r="F180" t="s">
         <v>11</v>
@@ -5860,7 +5128,7 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>378</v>
+        <v>255</v>
       </c>
       <c r="B181" t="s">
         <v>29</v>
@@ -5872,7 +5140,7 @@
         <v>30</v>
       </c>
       <c r="E181" t="s">
-        <v>379</v>
+        <v>43</v>
       </c>
       <c r="F181" t="s">
         <v>11</v>
@@ -5880,7 +5148,7 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>380</v>
+        <v>256</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
@@ -5892,7 +5160,7 @@
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>381</v>
+        <v>45</v>
       </c>
       <c r="F182" t="s">
         <v>11</v>
@@ -5900,7 +5168,7 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>382</v>
+        <v>257</v>
       </c>
       <c r="B183" t="s">
         <v>13</v>
@@ -5912,7 +5180,7 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>383</v>
+        <v>47</v>
       </c>
       <c r="F183" t="s">
         <v>11</v>
@@ -5920,7 +5188,7 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>384</v>
+        <v>258</v>
       </c>
       <c r="B184" t="s">
         <v>17</v>
@@ -5932,7 +5200,7 @@
         <v>18</v>
       </c>
       <c r="E184" t="s">
-        <v>385</v>
+        <v>49</v>
       </c>
       <c r="F184" t="s">
         <v>11</v>
@@ -5940,7 +5208,7 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>386</v>
+        <v>259</v>
       </c>
       <c r="B185" t="s">
         <v>21</v>
@@ -5952,7 +5220,7 @@
         <v>22</v>
       </c>
       <c r="E185" t="s">
-        <v>387</v>
+        <v>51</v>
       </c>
       <c r="F185" t="s">
         <v>11</v>
@@ -5960,7 +5228,7 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>388</v>
+        <v>260</v>
       </c>
       <c r="B186" t="s">
         <v>25</v>
@@ -5972,7 +5240,7 @@
         <v>26</v>
       </c>
       <c r="E186" t="s">
-        <v>389</v>
+        <v>53</v>
       </c>
       <c r="F186" t="s">
         <v>11</v>
@@ -5980,7 +5248,7 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>390</v>
+        <v>261</v>
       </c>
       <c r="B187" t="s">
         <v>29</v>
@@ -5992,7 +5260,7 @@
         <v>30</v>
       </c>
       <c r="E187" t="s">
-        <v>391</v>
+        <v>55</v>
       </c>
       <c r="F187" t="s">
         <v>11</v>
@@ -6000,7 +5268,7 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>392</v>
+        <v>262</v>
       </c>
       <c r="B188" t="s">
         <v>7</v>
@@ -6012,7 +5280,7 @@
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>393</v>
+        <v>57</v>
       </c>
       <c r="F188" t="s">
         <v>11</v>
@@ -6020,7 +5288,7 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>394</v>
+        <v>263</v>
       </c>
       <c r="B189" t="s">
         <v>13</v>
@@ -6032,7 +5300,7 @@
         <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>395</v>
+        <v>59</v>
       </c>
       <c r="F189" t="s">
         <v>11</v>
@@ -6040,7 +5308,7 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>396</v>
+        <v>264</v>
       </c>
       <c r="B190" t="s">
         <v>17</v>
@@ -6052,7 +5320,7 @@
         <v>18</v>
       </c>
       <c r="E190" t="s">
-        <v>397</v>
+        <v>61</v>
       </c>
       <c r="F190" t="s">
         <v>11</v>
@@ -6060,7 +5328,7 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>398</v>
+        <v>265</v>
       </c>
       <c r="B191" t="s">
         <v>21</v>
@@ -6072,7 +5340,7 @@
         <v>22</v>
       </c>
       <c r="E191" t="s">
-        <v>399</v>
+        <v>63</v>
       </c>
       <c r="F191" t="s">
         <v>11</v>
@@ -6080,7 +5348,7 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>400</v>
+        <v>266</v>
       </c>
       <c r="B192" t="s">
         <v>25</v>
@@ -6092,7 +5360,7 @@
         <v>26</v>
       </c>
       <c r="E192" t="s">
-        <v>401</v>
+        <v>65</v>
       </c>
       <c r="F192" t="s">
         <v>11</v>
@@ -6100,7 +5368,7 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>402</v>
+        <v>267</v>
       </c>
       <c r="B193" t="s">
         <v>29</v>
@@ -6112,7 +5380,7 @@
         <v>30</v>
       </c>
       <c r="E193" t="s">
-        <v>403</v>
+        <v>67</v>
       </c>
       <c r="F193" t="s">
         <v>11</v>
@@ -6120,7 +5388,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>404</v>
+        <v>268</v>
       </c>
       <c r="B194" t="s">
         <v>7</v>
@@ -6132,7 +5400,7 @@
         <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>405</v>
+        <v>69</v>
       </c>
       <c r="F194" t="s">
         <v>11</v>
@@ -6140,7 +5408,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>406</v>
+        <v>269</v>
       </c>
       <c r="B195" t="s">
         <v>13</v>
@@ -6152,7 +5420,7 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>407</v>
+        <v>71</v>
       </c>
       <c r="F195" t="s">
         <v>11</v>
@@ -6160,7 +5428,7 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>408</v>
+        <v>270</v>
       </c>
       <c r="B196" t="s">
         <v>17</v>
@@ -6172,7 +5440,7 @@
         <v>18</v>
       </c>
       <c r="E196" t="s">
-        <v>409</v>
+        <v>73</v>
       </c>
       <c r="F196" t="s">
         <v>11</v>
@@ -6180,7 +5448,7 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>410</v>
+        <v>271</v>
       </c>
       <c r="B197" t="s">
         <v>21</v>
@@ -6192,7 +5460,7 @@
         <v>22</v>
       </c>
       <c r="E197" t="s">
-        <v>411</v>
+        <v>75</v>
       </c>
       <c r="F197" t="s">
         <v>11</v>
@@ -6200,7 +5468,7 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>412</v>
+        <v>272</v>
       </c>
       <c r="B198" t="s">
         <v>25</v>
@@ -6212,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="E198" t="s">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="F198" t="s">
         <v>11</v>
@@ -6220,7 +5488,7 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>414</v>
+        <v>273</v>
       </c>
       <c r="B199" t="s">
         <v>29</v>
@@ -6232,7 +5500,7 @@
         <v>30</v>
       </c>
       <c r="E199" t="s">
-        <v>415</v>
+        <v>79</v>
       </c>
       <c r="F199" t="s">
         <v>11</v>
@@ -6240,7 +5508,7 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>416</v>
+        <v>274</v>
       </c>
       <c r="B200" t="s">
         <v>7</v>
@@ -6252,7 +5520,7 @@
         <v>9</v>
       </c>
       <c r="E200" t="s">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="F200" t="s">
         <v>11</v>
@@ -6260,7 +5528,7 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>418</v>
+        <v>275</v>
       </c>
       <c r="B201" t="s">
         <v>13</v>
@@ -6272,7 +5540,7 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="F201" t="s">
         <v>11</v>
@@ -6280,7 +5548,7 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>420</v>
+        <v>276</v>
       </c>
       <c r="B202" t="s">
         <v>17</v>
@@ -6292,7 +5560,7 @@
         <v>18</v>
       </c>
       <c r="E202" t="s">
-        <v>421</v>
+        <v>85</v>
       </c>
       <c r="F202" t="s">
         <v>11</v>
@@ -6300,7 +5568,7 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>422</v>
+        <v>277</v>
       </c>
       <c r="B203" t="s">
         <v>21</v>
@@ -6312,7 +5580,7 @@
         <v>22</v>
       </c>
       <c r="E203" t="s">
-        <v>423</v>
+        <v>87</v>
       </c>
       <c r="F203" t="s">
         <v>11</v>
@@ -6320,7 +5588,7 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>424</v>
+        <v>278</v>
       </c>
       <c r="B204" t="s">
         <v>25</v>
@@ -6332,7 +5600,7 @@
         <v>26</v>
       </c>
       <c r="E204" t="s">
-        <v>425</v>
+        <v>89</v>
       </c>
       <c r="F204" t="s">
         <v>11</v>
@@ -6340,7 +5608,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>426</v>
+        <v>279</v>
       </c>
       <c r="B205" t="s">
         <v>29</v>
@@ -6352,7 +5620,7 @@
         <v>30</v>
       </c>
       <c r="E205" t="s">
-        <v>427</v>
+        <v>91</v>
       </c>
       <c r="F205" t="s">
         <v>11</v>
@@ -6360,7 +5628,7 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>428</v>
+        <v>280</v>
       </c>
       <c r="B206" t="s">
         <v>7</v>
@@ -6372,7 +5640,7 @@
         <v>9</v>
       </c>
       <c r="E206" t="s">
-        <v>429</v>
+        <v>93</v>
       </c>
       <c r="F206" t="s">
         <v>11</v>
@@ -6380,7 +5648,7 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>430</v>
+        <v>281</v>
       </c>
       <c r="B207" t="s">
         <v>13</v>
@@ -6392,7 +5660,7 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>431</v>
+        <v>95</v>
       </c>
       <c r="F207" t="s">
         <v>11</v>
@@ -6400,7 +5668,7 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>432</v>
+        <v>282</v>
       </c>
       <c r="B208" t="s">
         <v>17</v>
@@ -6412,7 +5680,7 @@
         <v>18</v>
       </c>
       <c r="E208" t="s">
-        <v>433</v>
+        <v>97</v>
       </c>
       <c r="F208" t="s">
         <v>11</v>
@@ -6420,7 +5688,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>434</v>
+        <v>283</v>
       </c>
       <c r="B209" t="s">
         <v>21</v>
@@ -6432,7 +5700,7 @@
         <v>22</v>
       </c>
       <c r="E209" t="s">
-        <v>435</v>
+        <v>99</v>
       </c>
       <c r="F209" t="s">
         <v>11</v>
@@ -6440,7 +5708,7 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>436</v>
+        <v>284</v>
       </c>
       <c r="B210" t="s">
         <v>25</v>
@@ -6452,7 +5720,7 @@
         <v>26</v>
       </c>
       <c r="E210" t="s">
-        <v>437</v>
+        <v>101</v>
       </c>
       <c r="F210" t="s">
         <v>11</v>
@@ -6460,7 +5728,7 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>438</v>
+        <v>285</v>
       </c>
       <c r="B211" t="s">
         <v>29</v>
@@ -6472,7 +5740,7 @@
         <v>30</v>
       </c>
       <c r="E211" t="s">
-        <v>439</v>
+        <v>103</v>
       </c>
       <c r="F211" t="s">
         <v>11</v>
@@ -6480,7 +5748,7 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>440</v>
+        <v>286</v>
       </c>
       <c r="B212" t="s">
         <v>7</v>
@@ -6492,7 +5760,7 @@
         <v>9</v>
       </c>
       <c r="E212" t="s">
-        <v>441</v>
+        <v>105</v>
       </c>
       <c r="F212" t="s">
         <v>11</v>
@@ -6500,7 +5768,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>442</v>
+        <v>287</v>
       </c>
       <c r="B213" t="s">
         <v>13</v>
@@ -6512,7 +5780,7 @@
         <v>14</v>
       </c>
       <c r="E213" t="s">
-        <v>443</v>
+        <v>107</v>
       </c>
       <c r="F213" t="s">
         <v>11</v>
@@ -6520,7 +5788,7 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>444</v>
+        <v>288</v>
       </c>
       <c r="B214" t="s">
         <v>17</v>
@@ -6532,7 +5800,7 @@
         <v>18</v>
       </c>
       <c r="E214" t="s">
-        <v>445</v>
+        <v>109</v>
       </c>
       <c r="F214" t="s">
         <v>11</v>
@@ -6540,7 +5808,7 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>446</v>
+        <v>289</v>
       </c>
       <c r="B215" t="s">
         <v>21</v>
@@ -6552,7 +5820,7 @@
         <v>22</v>
       </c>
       <c r="E215" t="s">
-        <v>447</v>
+        <v>111</v>
       </c>
       <c r="F215" t="s">
         <v>11</v>
@@ -6560,7 +5828,7 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>448</v>
+        <v>290</v>
       </c>
       <c r="B216" t="s">
         <v>25</v>
@@ -6572,7 +5840,7 @@
         <v>26</v>
       </c>
       <c r="E216" t="s">
-        <v>449</v>
+        <v>113</v>
       </c>
       <c r="F216" t="s">
         <v>11</v>
@@ -6580,7 +5848,7 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>450</v>
+        <v>291</v>
       </c>
       <c r="B217" t="s">
         <v>29</v>
@@ -6592,7 +5860,7 @@
         <v>30</v>
       </c>
       <c r="E217" t="s">
-        <v>451</v>
+        <v>115</v>
       </c>
       <c r="F217" t="s">
         <v>11</v>
@@ -6600,7 +5868,7 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>452</v>
+        <v>292</v>
       </c>
       <c r="B218" t="s">
         <v>7</v>
@@ -6612,7 +5880,7 @@
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="F218" t="s">
         <v>11</v>
@@ -6620,7 +5888,7 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>454</v>
+        <v>293</v>
       </c>
       <c r="B219" t="s">
         <v>13</v>
@@ -6632,7 +5900,7 @@
         <v>14</v>
       </c>
       <c r="E219" t="s">
-        <v>455</v>
+        <v>119</v>
       </c>
       <c r="F219" t="s">
         <v>11</v>
@@ -6640,7 +5908,7 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>456</v>
+        <v>294</v>
       </c>
       <c r="B220" t="s">
         <v>17</v>
@@ -6652,7 +5920,7 @@
         <v>18</v>
       </c>
       <c r="E220" t="s">
-        <v>457</v>
+        <v>121</v>
       </c>
       <c r="F220" t="s">
         <v>11</v>
@@ -6660,7 +5928,7 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>458</v>
+        <v>295</v>
       </c>
       <c r="B221" t="s">
         <v>21</v>
@@ -6672,7 +5940,7 @@
         <v>22</v>
       </c>
       <c r="E221" t="s">
-        <v>459</v>
+        <v>123</v>
       </c>
       <c r="F221" t="s">
         <v>11</v>
@@ -6680,7 +5948,7 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>460</v>
+        <v>296</v>
       </c>
       <c r="B222" t="s">
         <v>25</v>
@@ -6692,7 +5960,7 @@
         <v>26</v>
       </c>
       <c r="E222" t="s">
-        <v>461</v>
+        <v>125</v>
       </c>
       <c r="F222" t="s">
         <v>11</v>
@@ -6700,7 +5968,7 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>462</v>
+        <v>297</v>
       </c>
       <c r="B223" t="s">
         <v>29</v>
@@ -6712,7 +5980,7 @@
         <v>30</v>
       </c>
       <c r="E223" t="s">
-        <v>463</v>
+        <v>127</v>
       </c>
       <c r="F223" t="s">
         <v>11</v>
@@ -6720,7 +5988,7 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>464</v>
+        <v>298</v>
       </c>
       <c r="B224" t="s">
         <v>7</v>
@@ -6732,7 +6000,7 @@
         <v>9</v>
       </c>
       <c r="E224" t="s">
-        <v>465</v>
+        <v>129</v>
       </c>
       <c r="F224" t="s">
         <v>11</v>
@@ -6740,7 +6008,7 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>466</v>
+        <v>299</v>
       </c>
       <c r="B225" t="s">
         <v>13</v>
@@ -6752,7 +6020,7 @@
         <v>14</v>
       </c>
       <c r="E225" t="s">
-        <v>467</v>
+        <v>131</v>
       </c>
       <c r="F225" t="s">
         <v>11</v>
@@ -6760,7 +6028,7 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>468</v>
+        <v>300</v>
       </c>
       <c r="B226" t="s">
         <v>17</v>
@@ -6772,7 +6040,7 @@
         <v>18</v>
       </c>
       <c r="E226" t="s">
-        <v>469</v>
+        <v>10</v>
       </c>
       <c r="F226" t="s">
         <v>11</v>
@@ -6780,7 +6048,7 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>470</v>
+        <v>301</v>
       </c>
       <c r="B227" t="s">
         <v>21</v>
@@ -6792,7 +6060,7 @@
         <v>22</v>
       </c>
       <c r="E227" t="s">
-        <v>471</v>
+        <v>15</v>
       </c>
       <c r="F227" t="s">
         <v>11</v>
@@ -6800,7 +6068,7 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>472</v>
+        <v>302</v>
       </c>
       <c r="B228" t="s">
         <v>25</v>
@@ -6812,7 +6080,7 @@
         <v>26</v>
       </c>
       <c r="E228" t="s">
-        <v>473</v>
+        <v>19</v>
       </c>
       <c r="F228" t="s">
         <v>11</v>
@@ -6820,7 +6088,7 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>474</v>
+        <v>303</v>
       </c>
       <c r="B229" t="s">
         <v>29</v>
@@ -6832,7 +6100,7 @@
         <v>30</v>
       </c>
       <c r="E229" t="s">
-        <v>475</v>
+        <v>23</v>
       </c>
       <c r="F229" t="s">
         <v>11</v>
@@ -6840,7 +6108,7 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>476</v>
+        <v>304</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
@@ -6852,7 +6120,7 @@
         <v>9</v>
       </c>
       <c r="E230" t="s">
-        <v>477</v>
+        <v>27</v>
       </c>
       <c r="F230" t="s">
         <v>11</v>
@@ -6860,7 +6128,7 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>478</v>
+        <v>305</v>
       </c>
       <c r="B231" t="s">
         <v>13</v>
@@ -6872,7 +6140,7 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>479</v>
+        <v>31</v>
       </c>
       <c r="F231" t="s">
         <v>11</v>
@@ -6880,7 +6148,7 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>480</v>
+        <v>306</v>
       </c>
       <c r="B232" t="s">
         <v>17</v>
@@ -6892,7 +6160,7 @@
         <v>18</v>
       </c>
       <c r="E232" t="s">
-        <v>481</v>
+        <v>33</v>
       </c>
       <c r="F232" t="s">
         <v>11</v>
@@ -6900,7 +6168,7 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>482</v>
+        <v>307</v>
       </c>
       <c r="B233" t="s">
         <v>21</v>
@@ -6912,7 +6180,7 @@
         <v>22</v>
       </c>
       <c r="E233" t="s">
-        <v>483</v>
+        <v>35</v>
       </c>
       <c r="F233" t="s">
         <v>11</v>
@@ -6920,7 +6188,7 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>484</v>
+        <v>308</v>
       </c>
       <c r="B234" t="s">
         <v>25</v>
@@ -6932,7 +6200,7 @@
         <v>26</v>
       </c>
       <c r="E234" t="s">
-        <v>485</v>
+        <v>37</v>
       </c>
       <c r="F234" t="s">
         <v>11</v>
@@ -6940,7 +6208,7 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>486</v>
+        <v>309</v>
       </c>
       <c r="B235" t="s">
         <v>29</v>
@@ -6952,7 +6220,7 @@
         <v>30</v>
       </c>
       <c r="E235" t="s">
-        <v>487</v>
+        <v>39</v>
       </c>
       <c r="F235" t="s">
         <v>11</v>
@@ -6960,7 +6228,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>488</v>
+        <v>310</v>
       </c>
       <c r="B236" t="s">
         <v>7</v>
@@ -6972,7 +6240,7 @@
         <v>9</v>
       </c>
       <c r="E236" t="s">
-        <v>489</v>
+        <v>41</v>
       </c>
       <c r="F236" t="s">
         <v>11</v>
@@ -6980,7 +6248,7 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>490</v>
+        <v>311</v>
       </c>
       <c r="B237" t="s">
         <v>13</v>
@@ -6992,7 +6260,7 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>491</v>
+        <v>43</v>
       </c>
       <c r="F237" t="s">
         <v>11</v>
@@ -7000,7 +6268,7 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>492</v>
+        <v>312</v>
       </c>
       <c r="B238" t="s">
         <v>17</v>
@@ -7012,7 +6280,7 @@
         <v>18</v>
       </c>
       <c r="E238" t="s">
-        <v>493</v>
+        <v>45</v>
       </c>
       <c r="F238" t="s">
         <v>11</v>
@@ -7020,7 +6288,7 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>494</v>
+        <v>313</v>
       </c>
       <c r="B239" t="s">
         <v>21</v>
@@ -7032,7 +6300,7 @@
         <v>22</v>
       </c>
       <c r="E239" t="s">
-        <v>495</v>
+        <v>47</v>
       </c>
       <c r="F239" t="s">
         <v>11</v>
@@ -7040,7 +6308,7 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>496</v>
+        <v>314</v>
       </c>
       <c r="B240" t="s">
         <v>25</v>
@@ -7052,7 +6320,7 @@
         <v>26</v>
       </c>
       <c r="E240" t="s">
-        <v>497</v>
+        <v>49</v>
       </c>
       <c r="F240" t="s">
         <v>11</v>
@@ -7060,7 +6328,7 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>498</v>
+        <v>315</v>
       </c>
       <c r="B241" t="s">
         <v>29</v>
@@ -7072,7 +6340,7 @@
         <v>30</v>
       </c>
       <c r="E241" t="s">
-        <v>499</v>
+        <v>51</v>
       </c>
       <c r="F241" t="s">
         <v>11</v>
@@ -7080,7 +6348,7 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>500</v>
+        <v>316</v>
       </c>
       <c r="B242" t="s">
         <v>7</v>
@@ -7092,7 +6360,7 @@
         <v>9</v>
       </c>
       <c r="E242" t="s">
-        <v>501</v>
+        <v>53</v>
       </c>
       <c r="F242" t="s">
         <v>11</v>
@@ -7100,7 +6368,7 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>502</v>
+        <v>317</v>
       </c>
       <c r="B243" t="s">
         <v>13</v>
@@ -7112,7 +6380,7 @@
         <v>14</v>
       </c>
       <c r="E243" t="s">
-        <v>503</v>
+        <v>55</v>
       </c>
       <c r="F243" t="s">
         <v>11</v>
@@ -7120,7 +6388,7 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>504</v>
+        <v>318</v>
       </c>
       <c r="B244" t="s">
         <v>17</v>
@@ -7132,7 +6400,7 @@
         <v>18</v>
       </c>
       <c r="E244" t="s">
-        <v>505</v>
+        <v>57</v>
       </c>
       <c r="F244" t="s">
         <v>11</v>
@@ -7140,7 +6408,7 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>506</v>
+        <v>319</v>
       </c>
       <c r="B245" t="s">
         <v>21</v>
@@ -7152,7 +6420,7 @@
         <v>22</v>
       </c>
       <c r="E245" t="s">
-        <v>507</v>
+        <v>59</v>
       </c>
       <c r="F245" t="s">
         <v>11</v>
@@ -7160,7 +6428,7 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>508</v>
+        <v>320</v>
       </c>
       <c r="B246" t="s">
         <v>25</v>
@@ -7172,7 +6440,7 @@
         <v>26</v>
       </c>
       <c r="E246" t="s">
-        <v>509</v>
+        <v>61</v>
       </c>
       <c r="F246" t="s">
         <v>11</v>
@@ -7180,7 +6448,7 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>510</v>
+        <v>321</v>
       </c>
       <c r="B247" t="s">
         <v>29</v>
@@ -7192,7 +6460,7 @@
         <v>30</v>
       </c>
       <c r="E247" t="s">
-        <v>511</v>
+        <v>63</v>
       </c>
       <c r="F247" t="s">
         <v>11</v>
@@ -7200,7 +6468,7 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>512</v>
+        <v>322</v>
       </c>
       <c r="B248" t="s">
         <v>7</v>
@@ -7212,7 +6480,7 @@
         <v>9</v>
       </c>
       <c r="E248" t="s">
-        <v>513</v>
+        <v>65</v>
       </c>
       <c r="F248" t="s">
         <v>11</v>
@@ -7220,7 +6488,7 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>514</v>
+        <v>323</v>
       </c>
       <c r="B249" t="s">
         <v>13</v>
@@ -7232,7 +6500,7 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
-        <v>515</v>
+        <v>67</v>
       </c>
       <c r="F249" t="s">
         <v>11</v>
@@ -7240,7 +6508,7 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>516</v>
+        <v>324</v>
       </c>
       <c r="B250" t="s">
         <v>17</v>
@@ -7252,7 +6520,7 @@
         <v>18</v>
       </c>
       <c r="E250" t="s">
-        <v>517</v>
+        <v>69</v>
       </c>
       <c r="F250" t="s">
         <v>11</v>
@@ -7260,7 +6528,7 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>518</v>
+        <v>325</v>
       </c>
       <c r="B251" t="s">
         <v>21</v>
@@ -7272,7 +6540,7 @@
         <v>22</v>
       </c>
       <c r="E251" t="s">
-        <v>519</v>
+        <v>71</v>
       </c>
       <c r="F251" t="s">
         <v>11</v>
@@ -7280,7 +6548,7 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="B252" t="s">
         <v>25</v>
@@ -7292,7 +6560,7 @@
         <v>26</v>
       </c>
       <c r="E252" t="s">
-        <v>521</v>
+        <v>73</v>
       </c>
       <c r="F252" t="s">
         <v>11</v>
@@ -7300,7 +6568,7 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>522</v>
+        <v>327</v>
       </c>
       <c r="B253" t="s">
         <v>29</v>
@@ -7312,7 +6580,7 @@
         <v>30</v>
       </c>
       <c r="E253" t="s">
-        <v>523</v>
+        <v>75</v>
       </c>
       <c r="F253" t="s">
         <v>11</v>
@@ -7320,7 +6588,7 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>524</v>
+        <v>328</v>
       </c>
       <c r="B254" t="s">
         <v>7</v>
@@ -7332,7 +6600,7 @@
         <v>9</v>
       </c>
       <c r="E254" t="s">
-        <v>525</v>
+        <v>77</v>
       </c>
       <c r="F254" t="s">
         <v>11</v>
@@ -7340,7 +6608,7 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>526</v>
+        <v>329</v>
       </c>
       <c r="B255" t="s">
         <v>13</v>
@@ -7352,7 +6620,7 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
-        <v>527</v>
+        <v>79</v>
       </c>
       <c r="F255" t="s">
         <v>11</v>
@@ -7360,7 +6628,7 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>528</v>
+        <v>330</v>
       </c>
       <c r="B256" t="s">
         <v>17</v>
@@ -7372,7 +6640,7 @@
         <v>18</v>
       </c>
       <c r="E256" t="s">
-        <v>529</v>
+        <v>81</v>
       </c>
       <c r="F256" t="s">
         <v>11</v>
@@ -7380,7 +6648,7 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>530</v>
+        <v>331</v>
       </c>
       <c r="B257" t="s">
         <v>21</v>
@@ -7392,7 +6660,7 @@
         <v>22</v>
       </c>
       <c r="E257" t="s">
-        <v>531</v>
+        <v>83</v>
       </c>
       <c r="F257" t="s">
         <v>11</v>
@@ -7400,7 +6668,7 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>532</v>
+        <v>332</v>
       </c>
       <c r="B258" t="s">
         <v>25</v>
@@ -7412,7 +6680,7 @@
         <v>26</v>
       </c>
       <c r="E258" t="s">
-        <v>533</v>
+        <v>85</v>
       </c>
       <c r="F258" t="s">
         <v>11</v>
@@ -7420,7 +6688,7 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>534</v>
+        <v>333</v>
       </c>
       <c r="B259" t="s">
         <v>29</v>
@@ -7432,7 +6700,7 @@
         <v>30</v>
       </c>
       <c r="E259" t="s">
-        <v>535</v>
+        <v>87</v>
       </c>
       <c r="F259" t="s">
         <v>11</v>
@@ -7440,7 +6708,7 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>536</v>
+        <v>334</v>
       </c>
       <c r="B260" t="s">
         <v>7</v>
@@ -7452,7 +6720,7 @@
         <v>9</v>
       </c>
       <c r="E260" t="s">
-        <v>537</v>
+        <v>89</v>
       </c>
       <c r="F260" t="s">
         <v>11</v>
@@ -7460,7 +6728,7 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>538</v>
+        <v>335</v>
       </c>
       <c r="B261" t="s">
         <v>13</v>
@@ -7472,7 +6740,7 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
-        <v>539</v>
+        <v>91</v>
       </c>
       <c r="F261" t="s">
         <v>11</v>
@@ -7480,7 +6748,7 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>540</v>
+        <v>336</v>
       </c>
       <c r="B262" t="s">
         <v>17</v>
@@ -7492,7 +6760,7 @@
         <v>18</v>
       </c>
       <c r="E262" t="s">
-        <v>541</v>
+        <v>93</v>
       </c>
       <c r="F262" t="s">
         <v>11</v>
@@ -7500,7 +6768,7 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>542</v>
+        <v>337</v>
       </c>
       <c r="B263" t="s">
         <v>21</v>
@@ -7512,7 +6780,7 @@
         <v>22</v>
       </c>
       <c r="E263" t="s">
-        <v>543</v>
+        <v>95</v>
       </c>
       <c r="F263" t="s">
         <v>11</v>
@@ -7520,7 +6788,7 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>544</v>
+        <v>338</v>
       </c>
       <c r="B264" t="s">
         <v>25</v>
@@ -7532,7 +6800,7 @@
         <v>26</v>
       </c>
       <c r="E264" t="s">
-        <v>545</v>
+        <v>97</v>
       </c>
       <c r="F264" t="s">
         <v>11</v>
@@ -7540,7 +6808,7 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>546</v>
+        <v>339</v>
       </c>
       <c r="B265" t="s">
         <v>29</v>
@@ -7552,7 +6820,7 @@
         <v>30</v>
       </c>
       <c r="E265" t="s">
-        <v>547</v>
+        <v>99</v>
       </c>
       <c r="F265" t="s">
         <v>11</v>
@@ -7560,7 +6828,7 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>548</v>
+        <v>340</v>
       </c>
       <c r="B266" t="s">
         <v>7</v>
@@ -7572,7 +6840,7 @@
         <v>9</v>
       </c>
       <c r="E266" t="s">
-        <v>549</v>
+        <v>101</v>
       </c>
       <c r="F266" t="s">
         <v>11</v>
@@ -7580,7 +6848,7 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>550</v>
+        <v>341</v>
       </c>
       <c r="B267" t="s">
         <v>13</v>
@@ -7592,7 +6860,7 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
-        <v>551</v>
+        <v>103</v>
       </c>
       <c r="F267" t="s">
         <v>11</v>
@@ -7600,7 +6868,7 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>552</v>
+        <v>342</v>
       </c>
       <c r="B268" t="s">
         <v>17</v>
@@ -7612,7 +6880,7 @@
         <v>18</v>
       </c>
       <c r="E268" t="s">
-        <v>553</v>
+        <v>105</v>
       </c>
       <c r="F268" t="s">
         <v>11</v>
@@ -7620,7 +6888,7 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>554</v>
+        <v>343</v>
       </c>
       <c r="B269" t="s">
         <v>21</v>
@@ -7632,7 +6900,7 @@
         <v>22</v>
       </c>
       <c r="E269" t="s">
-        <v>555</v>
+        <v>107</v>
       </c>
       <c r="F269" t="s">
         <v>11</v>
@@ -7640,7 +6908,7 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>556</v>
+        <v>344</v>
       </c>
       <c r="B270" t="s">
         <v>25</v>
@@ -7652,7 +6920,7 @@
         <v>26</v>
       </c>
       <c r="E270" t="s">
-        <v>557</v>
+        <v>109</v>
       </c>
       <c r="F270" t="s">
         <v>11</v>
@@ -7660,7 +6928,7 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>558</v>
+        <v>345</v>
       </c>
       <c r="B271" t="s">
         <v>29</v>
@@ -7672,7 +6940,7 @@
         <v>30</v>
       </c>
       <c r="E271" t="s">
-        <v>559</v>
+        <v>111</v>
       </c>
       <c r="F271" t="s">
         <v>11</v>
@@ -7680,7 +6948,7 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>560</v>
+        <v>346</v>
       </c>
       <c r="B272" t="s">
         <v>7</v>
@@ -7692,7 +6960,7 @@
         <v>9</v>
       </c>
       <c r="E272" t="s">
-        <v>561</v>
+        <v>113</v>
       </c>
       <c r="F272" t="s">
         <v>11</v>
@@ -7700,7 +6968,7 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>562</v>
+        <v>347</v>
       </c>
       <c r="B273" t="s">
         <v>13</v>
@@ -7712,7 +6980,7 @@
         <v>14</v>
       </c>
       <c r="E273" t="s">
-        <v>563</v>
+        <v>115</v>
       </c>
       <c r="F273" t="s">
         <v>11</v>
@@ -7720,7 +6988,7 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>564</v>
+        <v>348</v>
       </c>
       <c r="B274" t="s">
         <v>17</v>
@@ -7732,7 +7000,7 @@
         <v>18</v>
       </c>
       <c r="E274" t="s">
-        <v>565</v>
+        <v>117</v>
       </c>
       <c r="F274" t="s">
         <v>11</v>
@@ -7740,7 +7008,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>566</v>
+        <v>349</v>
       </c>
       <c r="B275" t="s">
         <v>21</v>
@@ -7752,7 +7020,7 @@
         <v>22</v>
       </c>
       <c r="E275" t="s">
-        <v>567</v>
+        <v>119</v>
       </c>
       <c r="F275" t="s">
         <v>11</v>
@@ -7760,7 +7028,7 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>568</v>
+        <v>350</v>
       </c>
       <c r="B276" t="s">
         <v>25</v>
@@ -7772,7 +7040,7 @@
         <v>26</v>
       </c>
       <c r="E276" t="s">
-        <v>569</v>
+        <v>121</v>
       </c>
       <c r="F276" t="s">
         <v>11</v>
@@ -7780,7 +7048,7 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>570</v>
+        <v>351</v>
       </c>
       <c r="B277" t="s">
         <v>29</v>
@@ -7792,7 +7060,7 @@
         <v>30</v>
       </c>
       <c r="E277" t="s">
-        <v>571</v>
+        <v>123</v>
       </c>
       <c r="F277" t="s">
         <v>11</v>
@@ -7800,7 +7068,7 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>572</v>
+        <v>352</v>
       </c>
       <c r="B278" t="s">
         <v>7</v>
@@ -7812,7 +7080,7 @@
         <v>9</v>
       </c>
       <c r="E278" t="s">
-        <v>573</v>
+        <v>125</v>
       </c>
       <c r="F278" t="s">
         <v>11</v>
@@ -7820,7 +7088,7 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>574</v>
+        <v>353</v>
       </c>
       <c r="B279" t="s">
         <v>13</v>
@@ -7832,7 +7100,7 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
-        <v>575</v>
+        <v>127</v>
       </c>
       <c r="F279" t="s">
         <v>11</v>
@@ -7840,7 +7108,7 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>576</v>
+        <v>354</v>
       </c>
       <c r="B280" t="s">
         <v>17</v>
@@ -7852,7 +7120,7 @@
         <v>18</v>
       </c>
       <c r="E280" t="s">
-        <v>577</v>
+        <v>129</v>
       </c>
       <c r="F280" t="s">
         <v>11</v>
@@ -7860,7 +7128,7 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>578</v>
+        <v>355</v>
       </c>
       <c r="B281" t="s">
         <v>21</v>
@@ -7872,7 +7140,7 @@
         <v>22</v>
       </c>
       <c r="E281" t="s">
-        <v>579</v>
+        <v>131</v>
       </c>
       <c r="F281" t="s">
         <v>11</v>
@@ -7880,7 +7148,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="B282" t="s">
         <v>25</v>
@@ -7892,7 +7160,7 @@
         <v>26</v>
       </c>
       <c r="E282" t="s">
-        <v>581</v>
+        <v>10</v>
       </c>
       <c r="F282" t="s">
         <v>11</v>
@@ -7900,7 +7168,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>582</v>
+        <v>357</v>
       </c>
       <c r="B283" t="s">
         <v>29</v>
@@ -7912,7 +7180,7 @@
         <v>30</v>
       </c>
       <c r="E283" t="s">
-        <v>583</v>
+        <v>15</v>
       </c>
       <c r="F283" t="s">
         <v>11</v>
@@ -7920,7 +7188,7 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>584</v>
+        <v>358</v>
       </c>
       <c r="B284" t="s">
         <v>7</v>
@@ -7932,7 +7200,7 @@
         <v>9</v>
       </c>
       <c r="E284" t="s">
-        <v>585</v>
+        <v>19</v>
       </c>
       <c r="F284" t="s">
         <v>11</v>
@@ -7940,7 +7208,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>586</v>
+        <v>359</v>
       </c>
       <c r="B285" t="s">
         <v>13</v>
@@ -7952,7 +7220,7 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
-        <v>587</v>
+        <v>23</v>
       </c>
       <c r="F285" t="s">
         <v>11</v>
@@ -7960,7 +7228,7 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>588</v>
+        <v>360</v>
       </c>
       <c r="B286" t="s">
         <v>17</v>
@@ -7972,7 +7240,7 @@
         <v>18</v>
       </c>
       <c r="E286" t="s">
-        <v>589</v>
+        <v>27</v>
       </c>
       <c r="F286" t="s">
         <v>11</v>
@@ -7980,7 +7248,7 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>590</v>
+        <v>361</v>
       </c>
       <c r="B287" t="s">
         <v>21</v>
@@ -7992,7 +7260,7 @@
         <v>22</v>
       </c>
       <c r="E287" t="s">
-        <v>591</v>
+        <v>31</v>
       </c>
       <c r="F287" t="s">
         <v>11</v>
@@ -8000,7 +7268,7 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>592</v>
+        <v>362</v>
       </c>
       <c r="B288" t="s">
         <v>25</v>
@@ -8012,7 +7280,7 @@
         <v>26</v>
       </c>
       <c r="E288" t="s">
-        <v>593</v>
+        <v>33</v>
       </c>
       <c r="F288" t="s">
         <v>11</v>
@@ -8020,7 +7288,7 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>594</v>
+        <v>363</v>
       </c>
       <c r="B289" t="s">
         <v>29</v>
@@ -8032,7 +7300,7 @@
         <v>30</v>
       </c>
       <c r="E289" t="s">
-        <v>595</v>
+        <v>35</v>
       </c>
       <c r="F289" t="s">
         <v>11</v>
@@ -8040,7 +7308,7 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>596</v>
+        <v>364</v>
       </c>
       <c r="B290" t="s">
         <v>7</v>
@@ -8052,7 +7320,7 @@
         <v>9</v>
       </c>
       <c r="E290" t="s">
-        <v>597</v>
+        <v>37</v>
       </c>
       <c r="F290" t="s">
         <v>11</v>
@@ -8060,7 +7328,7 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>598</v>
+        <v>365</v>
       </c>
       <c r="B291" t="s">
         <v>13</v>
@@ -8072,7 +7340,7 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
-        <v>599</v>
+        <v>39</v>
       </c>
       <c r="F291" t="s">
         <v>11</v>
@@ -8080,7 +7348,7 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="B292" t="s">
         <v>17</v>
@@ -8092,7 +7360,7 @@
         <v>18</v>
       </c>
       <c r="E292" t="s">
-        <v>601</v>
+        <v>41</v>
       </c>
       <c r="F292" t="s">
         <v>11</v>
@@ -8100,7 +7368,7 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>602</v>
+        <v>367</v>
       </c>
       <c r="B293" t="s">
         <v>21</v>
@@ -8112,7 +7380,7 @@
         <v>22</v>
       </c>
       <c r="E293" t="s">
-        <v>603</v>
+        <v>43</v>
       </c>
       <c r="F293" t="s">
         <v>11</v>
@@ -8120,7 +7388,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>604</v>
+        <v>368</v>
       </c>
       <c r="B294" t="s">
         <v>25</v>
@@ -8132,7 +7400,7 @@
         <v>26</v>
       </c>
       <c r="E294" t="s">
-        <v>605</v>
+        <v>45</v>
       </c>
       <c r="F294" t="s">
         <v>11</v>
@@ -8140,7 +7408,7 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>606</v>
+        <v>369</v>
       </c>
       <c r="B295" t="s">
         <v>29</v>
@@ -8152,7 +7420,7 @@
         <v>30</v>
       </c>
       <c r="E295" t="s">
-        <v>607</v>
+        <v>47</v>
       </c>
       <c r="F295" t="s">
         <v>11</v>
@@ -8160,7 +7428,7 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>608</v>
+        <v>370</v>
       </c>
       <c r="B296" t="s">
         <v>7</v>
@@ -8172,7 +7440,7 @@
         <v>9</v>
       </c>
       <c r="E296" t="s">
-        <v>609</v>
+        <v>49</v>
       </c>
       <c r="F296" t="s">
         <v>11</v>
@@ -8180,7 +7448,7 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>610</v>
+        <v>371</v>
       </c>
       <c r="B297" t="s">
         <v>13</v>
@@ -8192,7 +7460,7 @@
         <v>14</v>
       </c>
       <c r="E297" t="s">
-        <v>611</v>
+        <v>51</v>
       </c>
       <c r="F297" t="s">
         <v>11</v>
@@ -8200,7 +7468,7 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>612</v>
+        <v>372</v>
       </c>
       <c r="B298" t="s">
         <v>17</v>
@@ -8212,7 +7480,7 @@
         <v>18</v>
       </c>
       <c r="E298" t="s">
-        <v>613</v>
+        <v>53</v>
       </c>
       <c r="F298" t="s">
         <v>11</v>
@@ -8220,7 +7488,7 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>614</v>
+        <v>373</v>
       </c>
       <c r="B299" t="s">
         <v>21</v>
@@ -8232,7 +7500,7 @@
         <v>22</v>
       </c>
       <c r="E299" t="s">
-        <v>615</v>
+        <v>55</v>
       </c>
       <c r="F299" t="s">
         <v>11</v>
@@ -8240,7 +7508,7 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>616</v>
+        <v>374</v>
       </c>
       <c r="B300" t="s">
         <v>25</v>
@@ -8252,7 +7520,7 @@
         <v>26</v>
       </c>
       <c r="E300" t="s">
-        <v>617</v>
+        <v>57</v>
       </c>
       <c r="F300" t="s">
         <v>11</v>
@@ -8260,7 +7528,7 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>618</v>
+        <v>375</v>
       </c>
       <c r="B301" t="s">
         <v>29</v>
@@ -8272,7 +7540,7 @@
         <v>30</v>
       </c>
       <c r="E301" t="s">
-        <v>619</v>
+        <v>59</v>
       </c>
       <c r="F301" t="s">
         <v>11</v>

--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -43,7 +43,7 @@
     <t>Repository Roots</t>
   </si>
   <si>
-    <t>Verify that Semgrep static audit on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that Semgrep static audit on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>PASSED</t>
@@ -58,7 +58,7 @@
     <t>frontend/package.json</t>
   </si>
   <si>
-    <t>Verify that Trivy filesystem scan on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that Trivy filesystem scan on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-003</t>
@@ -70,7 +70,7 @@
     <t>backend/app</t>
   </si>
   <si>
-    <t>Verify that Gitleaks secret search on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that Gitleaks secret search on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-004</t>
@@ -82,7 +82,7 @@
     <t>backend/requirements.txt</t>
   </si>
   <si>
-    <t>Verify that npm dependency audit on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that npm dependency audit on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-005</t>
@@ -94,7 +94,7 @@
     <t>docker/compose.yml</t>
   </si>
   <si>
-    <t>Verify that pip package audit on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that pip package audit on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-006</t>
@@ -106,307 +106,307 @@
     <t>infrastructure/gcp</t>
   </si>
   <si>
-    <t>Verify that OWASP security compliance on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that OWASP security compliance on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-007</t>
   </si>
   <si>
-    <t>Verify that Input sanitation checking on database migration history is resolving directory traversal checks</t>
+    <t>Verify that Input sanitation checking on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-008</t>
   </si>
   <si>
-    <t>Verify that CORS security verification on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that CORS security verification on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>SEC-009</t>
   </si>
   <si>
-    <t>Verify that Semgrep static audit on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that Semgrep static audit on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-010</t>
   </si>
   <si>
-    <t>Verify that Trivy filesystem scan on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that Trivy filesystem scan on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-011</t>
   </si>
   <si>
-    <t>Verify that Gitleaks secret search on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that Gitleaks secret search on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-012</t>
   </si>
   <si>
-    <t>Verify that npm dependency audit on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that npm dependency audit on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-013</t>
   </si>
   <si>
-    <t>Verify that pip package audit on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that pip package audit on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-014</t>
   </si>
   <si>
-    <t>Verify that OWASP security compliance on database migration history is resolving directory traversal checks</t>
+    <t>Verify that OWASP security compliance on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-015</t>
   </si>
   <si>
-    <t>Verify that Input sanitation checking on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that Input sanitation checking on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>SEC-016</t>
   </si>
   <si>
-    <t>Verify that CORS security verification on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that CORS security verification on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-017</t>
   </si>
   <si>
-    <t>Verify that Semgrep static audit on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that Semgrep static audit on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-018</t>
   </si>
   <si>
-    <t>Verify that Trivy filesystem scan on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that Trivy filesystem scan on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-019</t>
   </si>
   <si>
-    <t>Verify that Gitleaks secret search on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that Gitleaks secret search on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-020</t>
   </si>
   <si>
-    <t>Verify that npm dependency audit on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that npm dependency audit on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-021</t>
   </si>
   <si>
-    <t>Verify that pip package audit on database migration history is resolving directory traversal checks</t>
+    <t>Verify that pip package audit on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-022</t>
   </si>
   <si>
-    <t>Verify that OWASP security compliance on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that OWASP security compliance on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>SEC-023</t>
   </si>
   <si>
-    <t>Verify that Input sanitation checking on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that Input sanitation checking on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-024</t>
   </si>
   <si>
-    <t>Verify that CORS security verification on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that CORS security verification on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-025</t>
   </si>
   <si>
-    <t>Verify that Semgrep static audit on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that Semgrep static audit on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-026</t>
   </si>
   <si>
-    <t>Verify that Trivy filesystem scan on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that Trivy filesystem scan on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-027</t>
   </si>
   <si>
-    <t>Verify that Gitleaks secret search on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that Gitleaks secret search on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-028</t>
   </si>
   <si>
-    <t>Verify that npm dependency audit on database migration history is resolving directory traversal checks</t>
+    <t>Verify that npm dependency audit on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-029</t>
   </si>
   <si>
-    <t>Verify that pip package audit on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that pip package audit on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>SEC-030</t>
   </si>
   <si>
-    <t>Verify that OWASP security compliance on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that OWASP security compliance on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-031</t>
   </si>
   <si>
-    <t>Verify that Input sanitation checking on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that Input sanitation checking on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-032</t>
   </si>
   <si>
-    <t>Verify that CORS security verification on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that CORS security verification on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-033</t>
   </si>
   <si>
-    <t>Verify that Semgrep static audit on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that Semgrep static audit on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-034</t>
   </si>
   <si>
-    <t>Verify that Trivy filesystem scan on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that Trivy filesystem scan on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-035</t>
   </si>
   <si>
-    <t>Verify that Gitleaks secret search on database migration history is resolving directory traversal checks</t>
+    <t>Verify that Gitleaks secret search on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-036</t>
   </si>
   <si>
-    <t>Verify that npm dependency audit on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that npm dependency audit on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>SEC-037</t>
   </si>
   <si>
-    <t>Verify that pip package audit on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that pip package audit on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-038</t>
   </si>
   <si>
-    <t>Verify that OWASP security compliance on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that OWASP security compliance on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-039</t>
   </si>
   <si>
-    <t>Verify that Input sanitation checking on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that Input sanitation checking on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-040</t>
   </si>
   <si>
-    <t>Verify that CORS security verification on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that CORS security verification on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-041</t>
   </si>
   <si>
-    <t>Verify that Semgrep static audit on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that Semgrep static audit on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-042</t>
   </si>
   <si>
-    <t>Verify that Trivy filesystem scan on database migration history is resolving directory traversal checks</t>
+    <t>Verify that Trivy filesystem scan on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-043</t>
   </si>
   <si>
-    <t>Verify that Gitleaks secret search on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that Gitleaks secret search on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>SEC-044</t>
   </si>
   <si>
-    <t>Verify that npm dependency audit on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that npm dependency audit on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-045</t>
   </si>
   <si>
-    <t>Verify that pip package audit on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that pip package audit on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-046</t>
   </si>
   <si>
-    <t>Verify that OWASP security compliance on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that OWASP security compliance on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-047</t>
   </si>
   <si>
-    <t>Verify that Input sanitation checking on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that Input sanitation checking on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-048</t>
   </si>
   <si>
-    <t>Verify that CORS security verification on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that CORS security verification on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-049</t>
   </si>
   <si>
-    <t>Verify that Semgrep static audit on database migration history is resolving directory traversal checks</t>
+    <t>Verify that Semgrep static audit on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-050</t>
   </si>
   <si>
-    <t>Verify that Trivy filesystem scan on backend python app directory is confirming zero critical vulnerabilities</t>
+    <t>Verify that Trivy filesystem scan on backend python app directory is confirming zero critical vulnerabilities. Explanation: Runs vulnerability scanner to audit backend python app directory for security compliance, ensuring confirming zero critical vulnerabilities.</t>
   </si>
   <si>
     <t>SEC-051</t>
   </si>
   <si>
-    <t>Verify that Gitleaks secret search on frontend package dependencies is verifying no credentials exposure</t>
+    <t>Verify that Gitleaks secret search on frontend package dependencies is verifying no credentials exposure. Explanation: Runs vulnerability scanner to audit frontend package dependencies for security compliance, ensuring verifying no credentials exposure.</t>
   </si>
   <si>
     <t>SEC-052</t>
   </si>
   <si>
-    <t>Verify that npm dependency audit on git repository commit tree is validating input sanitization rules</t>
+    <t>Verify that npm dependency audit on git repository commit tree is validating input sanitization rules. Explanation: Runs vulnerability scanner to audit git repository commit tree for security compliance, ensuring validating input sanitization rules.</t>
   </si>
   <si>
     <t>SEC-053</t>
   </si>
   <si>
-    <t>Verify that pip package audit on REST endpoint query handlers is verifying secure dependency trees</t>
+    <t>Verify that pip package audit on REST endpoint query handlers is verifying secure dependency trees. Explanation: Runs vulnerability scanner to audit REST endpoint query handlers for security compliance, ensuring verifying secure dependency trees.</t>
   </si>
   <si>
     <t>SEC-054</t>
   </si>
   <si>
-    <t>Verify that OWASP security compliance on HTML template source pages is securing against SQL injection vectors</t>
+    <t>Verify that OWASP security compliance on HTML template source pages is securing against SQL injection vectors. Explanation: Runs vulnerability scanner to audit HTML template source pages for security compliance, ensuring securing against SQL injection vectors.</t>
   </si>
   <si>
     <t>SEC-055</t>
   </si>
   <si>
-    <t>Verify that Input sanitation checking on configuration env keys is enforcing safe cross origin policy</t>
+    <t>Verify that Input sanitation checking on configuration env keys is enforcing safe cross origin policy. Explanation: Runs vulnerability scanner to audit configuration env keys for security compliance, ensuring enforcing safe cross origin policy.</t>
   </si>
   <si>
     <t>SEC-056</t>
   </si>
   <si>
-    <t>Verify that CORS security verification on database migration history is resolving directory traversal checks</t>
+    <t>Verify that CORS security verification on database migration history is resolving directory traversal checks. Explanation: Runs vulnerability scanner to audit database migration history for security compliance, ensuring resolving directory traversal checks.</t>
   </si>
   <si>
     <t>SEC-057</t>
